--- a/model/Outputs/11. Interest rate/0/Output Files/0.2/Output_9_47.xlsx
+++ b/model/Outputs/11. Interest rate/0/Output Files/0.2/Output_9_47.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4292629.762544897</v>
+        <v>4328920.152355722</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13276484.54337385</v>
+        <v>13279501.51514058</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13276484.54337385</v>
+        <v>13279501.51514058</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>603.5370117101936</v>
+        <v>987.0883260126712</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>603.5370117101936</v>
+        <v>987.0883260126712</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20558299.47943874</v>
+        <v>20557546.73593489</v>
       </c>
     </row>
   </sheetData>
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>81.99931295557451</v>
+        <v>80.07191941636594</v>
       </c>
       <c r="C2" t="n">
         <v>49.47457824299391</v>
@@ -669,13 +669,13 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G2" t="n">
-        <v>3.34732203575993</v>
+        <v>3.343301935257443</v>
       </c>
       <c r="H2" t="n">
-        <v>3.81023156784903</v>
+        <v>3.769060713577687</v>
       </c>
       <c r="I2" t="n">
-        <v>1.79868786782652</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -705,13 +705,13 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>85.50414770182039</v>
+        <v>85.41253966161941</v>
       </c>
       <c r="T2" t="n">
-        <v>184.8805867536895</v>
+        <v>184.8629887637397</v>
       </c>
       <c r="U2" t="n">
-        <v>249.1884925285102</v>
+        <v>249.1881709204699</v>
       </c>
       <c r="V2" t="n">
         <v>229.8510241668239</v>
@@ -745,16 +745,16 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>330.0284079411381</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>209.4985557026693</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -778,25 +778,25 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>145.073529241423</v>
+        <v>144.7989632036872</v>
       </c>
       <c r="R3" t="n">
-        <v>133.6519859716245</v>
+        <v>286.6844089887153</v>
       </c>
       <c r="S3" t="n">
-        <v>62.48881128536601</v>
+        <v>62.44885845517734</v>
       </c>
       <c r="T3" t="n">
-        <v>16.14537157181693</v>
+        <v>4.464774651476091</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1959257979225981</v>
+        <v>0.1957842884886531</v>
       </c>
       <c r="V3" t="n">
         <v>14.51066719152016</v>
       </c>
       <c r="W3" t="n">
-        <v>374</v>
+        <v>32.37314290982852</v>
       </c>
       <c r="X3" t="n">
         <v>19.86273944538755</v>
@@ -845,22 +845,22 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>91.79905402550071</v>
+        <v>91.51638189435317</v>
       </c>
       <c r="N4" t="n">
-        <v>143.0380916651276</v>
+        <v>142.7621408454554</v>
       </c>
       <c r="O4" t="n">
-        <v>214.4472689970478</v>
+        <v>214.1923837511461</v>
       </c>
       <c r="P4" t="n">
-        <v>265.2018645413922</v>
+        <v>264.9837661807364</v>
       </c>
       <c r="Q4" t="n">
-        <v>310.437266425598</v>
+        <v>310.286266425598</v>
       </c>
       <c r="R4" t="n">
-        <v>318.3317673254134</v>
+        <v>318.2506853582003</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -906,13 +906,13 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G5" t="n">
-        <v>3.34732203575993</v>
+        <v>3.343301935257443</v>
       </c>
       <c r="H5" t="n">
-        <v>3.81023156784903</v>
+        <v>3.769060713577687</v>
       </c>
       <c r="I5" t="n">
-        <v>1.79868786782652</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -942,13 +942,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>85.50414770182039</v>
+        <v>87.36594612241093</v>
       </c>
       <c r="T5" t="n">
-        <v>184.8805867536895</v>
+        <v>184.8629887637397</v>
       </c>
       <c r="U5" t="n">
-        <v>249.1884925285102</v>
+        <v>249.1881709204699</v>
       </c>
       <c r="V5" t="n">
         <v>229.8510241668239</v>
@@ -976,7 +976,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>140.153575940087</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -1015,19 +1015,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>144.7989632036872</v>
       </c>
       <c r="R6" t="n">
-        <v>133.6519859716245</v>
+        <v>133.5184388018132</v>
       </c>
       <c r="S6" t="n">
-        <v>374</v>
+        <v>62.44885845517734</v>
       </c>
       <c r="T6" t="n">
-        <v>374</v>
+        <v>4.464774651476091</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1959257979225981</v>
+        <v>0.1957842884886531</v>
       </c>
       <c r="V6" t="n">
         <v>374</v>
@@ -1036,10 +1036,10 @@
         <v>32.37314290982852</v>
       </c>
       <c r="X6" t="n">
-        <v>19.86273944538755</v>
+        <v>374</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>325.4213222043793</v>
       </c>
     </row>
     <row r="7">
@@ -1082,22 +1082,22 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>91.79905402550071</v>
+        <v>91.51638189435317</v>
       </c>
       <c r="N7" t="n">
-        <v>143.0380916651276</v>
+        <v>142.7621408454554</v>
       </c>
       <c r="O7" t="n">
-        <v>214.4472689970478</v>
+        <v>214.1923837511461</v>
       </c>
       <c r="P7" t="n">
-        <v>265.2018645413922</v>
+        <v>264.9837661807364</v>
       </c>
       <c r="Q7" t="n">
-        <v>310.437266425598</v>
+        <v>310.286266425598</v>
       </c>
       <c r="R7" t="n">
-        <v>318.3317673254134</v>
+        <v>318.2506853582003</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1146,10 +1146,10 @@
         <v>3.343301935257443</v>
       </c>
       <c r="H8" t="n">
-        <v>3.769060713577687</v>
+        <v>5.722467174369123</v>
       </c>
       <c r="I8" t="n">
-        <v>1.953406460791434</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1210,22 +1210,22 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>227.9342447712888</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>325.517988705216</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>31.22158730246607</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1252,10 +1252,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>144.7989632036872</v>
       </c>
       <c r="R9" t="n">
-        <v>374</v>
+        <v>133.5184388018132</v>
       </c>
       <c r="S9" t="n">
         <v>62.44885845517734</v>
@@ -1264,13 +1264,13 @@
         <v>4.464774651476091</v>
       </c>
       <c r="U9" t="n">
-        <v>374</v>
+        <v>0.1957842884886531</v>
       </c>
       <c r="V9" t="n">
         <v>14.51066719152016</v>
       </c>
       <c r="W9" t="n">
-        <v>374</v>
+        <v>32.37314290982852</v>
       </c>
       <c r="X9" t="n">
         <v>19.86273944538755</v>
@@ -1380,10 +1380,10 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G11" t="n">
-        <v>81.3744577141519</v>
+        <v>81.37445771415189</v>
       </c>
       <c r="H11" t="n">
-        <v>73.30747219949504</v>
+        <v>73.30747219949482</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1447,22 +1447,22 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C12" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D12" t="n">
         <v>26.93768689770263</v>
       </c>
       <c r="E12" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F12" t="n">
         <v>18.63624233787687</v>
       </c>
       <c r="G12" t="n">
-        <v>324.9996113467254</v>
+        <v>98.96287911935127</v>
       </c>
       <c r="H12" t="n">
-        <v>4.021973978873973</v>
+        <v>4.021973978873961</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1489,28 +1489,28 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R12" t="n">
-        <v>180.333570877285</v>
+        <v>501.333570877285</v>
       </c>
       <c r="S12" t="n">
-        <v>131.8202263797057</v>
+        <v>452.8202263797057</v>
       </c>
       <c r="T12" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U12" t="n">
-        <v>79.16168051490371</v>
+        <v>79.16168051490372</v>
       </c>
       <c r="V12" t="n">
-        <v>267.1024830734931</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W12" t="n">
         <v>111.3731429098285</v>
       </c>
       <c r="X12" t="n">
-        <v>98.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y12" t="n">
         <v>78.39139276613435</v>
@@ -1553,10 +1553,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>9.483546242607703</v>
+        <v>10.3217920922054</v>
       </c>
       <c r="M13" t="n">
-        <v>102.3923982877958</v>
+        <v>101.5541524381981</v>
       </c>
       <c r="N13" t="n">
         <v>155.2579933044718</v>
@@ -1565,13 +1565,13 @@
         <v>231.765039488851</v>
       </c>
       <c r="P13" t="n">
-        <v>291.4220612627038</v>
+        <v>291.4220612627037</v>
       </c>
       <c r="Q13" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R13" t="n">
-        <v>377.7099312598395</v>
+        <v>377.7099312598396</v>
       </c>
       <c r="S13" t="n">
         <v>30.56285675203577</v>
@@ -1617,10 +1617,10 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G14" t="n">
-        <v>81.37445771415189</v>
+        <v>81.3744577141519</v>
       </c>
       <c r="H14" t="n">
-        <v>73.30747219949482</v>
+        <v>72.84688483418068</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1650,7 +1650,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>0.4605873653139497</v>
       </c>
       <c r="S14" t="n">
         <v>142.3350019731772</v>
@@ -1681,7 +1681,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C15" t="n">
         <v>40.09991244551929</v>
@@ -1690,16 +1690,16 @@
         <v>26.93768689770263</v>
       </c>
       <c r="E15" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F15" t="n">
         <v>18.63624233787687</v>
       </c>
       <c r="G15" t="n">
-        <v>3.999611346725456</v>
+        <v>324.9996113467254</v>
       </c>
       <c r="H15" t="n">
-        <v>4.021973978873961</v>
+        <v>177.613789860847</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1732,19 +1732,19 @@
         <v>180.333570877285</v>
       </c>
       <c r="S15" t="n">
-        <v>131.8202263797056</v>
+        <v>131.8202263797057</v>
       </c>
       <c r="T15" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U15" t="n">
-        <v>252.7534963968771</v>
+        <v>79.16168051490371</v>
       </c>
       <c r="V15" t="n">
         <v>93.51066719152016</v>
       </c>
       <c r="W15" t="n">
-        <v>432.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X15" t="n">
         <v>419.8627394453875</v>
@@ -1790,7 +1790,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>10.3217920922054</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M16" t="n">
         <v>102.3923982877958</v>
@@ -1802,16 +1802,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P16" t="n">
-        <v>291.4220612627037</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q16" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R16" t="n">
-        <v>377.7099312598396</v>
+        <v>377.7099312598395</v>
       </c>
       <c r="S16" t="n">
-        <v>29.72461090243842</v>
+        <v>29.72461090243831</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -1857,10 +1857,10 @@
         <v>81.3744577141519</v>
       </c>
       <c r="H17" t="n">
-        <v>73.30747219949504</v>
+        <v>72.84688483418068</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>0.4605873653143577</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>237.1483725282995</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C18" t="n">
-        <v>361.0999124455193</v>
+        <v>213.6917283274922</v>
       </c>
       <c r="D18" t="n">
         <v>347.9376868977026</v>
@@ -1930,7 +1930,7 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F18" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G18" t="n">
         <v>3.99961134672543</v>
@@ -2091,13 +2091,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G20" t="n">
-        <v>81.3744577141519</v>
+        <v>81.37445771415189</v>
       </c>
       <c r="H20" t="n">
         <v>72.84688483418068</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4605873653143577</v>
+        <v>0.4605873653141466</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2155,25 +2155,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>63.55655664632661</v>
+        <v>237.1483725282997</v>
       </c>
       <c r="C21" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D21" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E21" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F21" t="n">
         <v>18.63624233787687</v>
       </c>
       <c r="G21" t="n">
-        <v>3.99961134672543</v>
+        <v>3.999611346725456</v>
       </c>
       <c r="H21" t="n">
-        <v>4.021973978873973</v>
+        <v>4.021973978873961</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -2206,25 +2206,25 @@
         <v>180.333570877285</v>
       </c>
       <c r="S21" t="n">
-        <v>131.8202263797057</v>
+        <v>131.8202263797056</v>
       </c>
       <c r="T21" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U21" t="n">
-        <v>79.16168051490371</v>
+        <v>79.16168051490372</v>
       </c>
       <c r="V21" t="n">
-        <v>414.5106671915202</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W21" t="n">
         <v>111.3731429098285</v>
       </c>
       <c r="X21" t="n">
-        <v>419.8627394453875</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y21" t="n">
-        <v>251.9832086481079</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="22">
@@ -2264,7 +2264,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>10.32179209220538</v>
+        <v>9.483546242607703</v>
       </c>
       <c r="M22" t="n">
         <v>102.3923982877958</v>
@@ -2276,16 +2276,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P22" t="n">
-        <v>291.4220612627038</v>
+        <v>291.4220612627037</v>
       </c>
       <c r="Q22" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R22" t="n">
-        <v>377.7099312598395</v>
+        <v>377.7099312598396</v>
       </c>
       <c r="S22" t="n">
-        <v>29.72461090243831</v>
+        <v>30.56285675203577</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -2328,10 +2328,10 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G23" t="n">
-        <v>81.37445771415189</v>
+        <v>81.3744577141519</v>
       </c>
       <c r="H23" t="n">
-        <v>73.30747219949482</v>
+        <v>72.84688483418068</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2361,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>0.4605873653139497</v>
       </c>
       <c r="S23" t="n">
         <v>142.3350019731772</v>
@@ -2392,25 +2392,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>384.5565566463266</v>
+        <v>237.1483725282995</v>
       </c>
       <c r="C24" t="n">
         <v>40.09991244551929</v>
       </c>
       <c r="D24" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E24" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F24" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G24" t="n">
-        <v>3.999611346725456</v>
+        <v>3.99961134672543</v>
       </c>
       <c r="H24" t="n">
-        <v>4.021973978873961</v>
+        <v>4.021973978873973</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -2443,19 +2443,19 @@
         <v>180.333570877285</v>
       </c>
       <c r="S24" t="n">
-        <v>131.8202263797056</v>
+        <v>131.8202263797057</v>
       </c>
       <c r="T24" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U24" t="n">
-        <v>400.1616805149037</v>
+        <v>79.16168051490371</v>
       </c>
       <c r="V24" t="n">
-        <v>414.5106671915202</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W24" t="n">
-        <v>284.9649587918017</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X24" t="n">
         <v>98.86273944538755</v>
@@ -2501,7 +2501,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>10.3217920922054</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M25" t="n">
         <v>102.3923982877958</v>
@@ -2513,16 +2513,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P25" t="n">
-        <v>291.4220612627037</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q25" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R25" t="n">
-        <v>377.7099312598396</v>
+        <v>377.7099312598395</v>
       </c>
       <c r="S25" t="n">
-        <v>29.72461090243842</v>
+        <v>29.72461090243831</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -2571,7 +2571,7 @@
         <v>72.84688483418068</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4605873653141466</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2598,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>0.4605873653139497</v>
       </c>
       <c r="S26" t="n">
         <v>142.3350019731772</v>
@@ -2629,16 +2629,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>384.5565566463266</v>
+        <v>237.1483725282997</v>
       </c>
       <c r="C27" t="n">
-        <v>40.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D27" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E27" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F27" t="n">
         <v>18.63624233787687</v>
@@ -2650,7 +2650,7 @@
         <v>4.021973978873961</v>
       </c>
       <c r="I27" t="n">
-        <v>191.6509141932353</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2686,10 +2686,10 @@
         <v>81.3753501231742</v>
       </c>
       <c r="U27" t="n">
-        <v>400.1616805149037</v>
+        <v>79.16168051490372</v>
       </c>
       <c r="V27" t="n">
-        <v>396.4515688802578</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W27" t="n">
         <v>111.3731429098285</v>
@@ -2738,7 +2738,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>9.483546242607703</v>
+        <v>10.3217920922054</v>
       </c>
       <c r="M28" t="n">
         <v>102.3923982877958</v>
@@ -2759,7 +2759,7 @@
         <v>377.7099312598396</v>
       </c>
       <c r="S28" t="n">
-        <v>30.56285675203577</v>
+        <v>29.72461090243842</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -2802,10 +2802,10 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G29" t="n">
-        <v>81.3744577141519</v>
+        <v>81.37445771415189</v>
       </c>
       <c r="H29" t="n">
-        <v>72.84688483418068</v>
+        <v>73.30747219949482</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2835,7 +2835,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>0.4605873653139497</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>142.3350019731772</v>
@@ -2869,7 +2869,7 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C30" t="n">
-        <v>40.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D30" t="n">
         <v>26.93768689770263</v>
@@ -2878,13 +2878,13 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F30" t="n">
-        <v>339.6362423378769</v>
+        <v>192.2280582198502</v>
       </c>
       <c r="G30" t="n">
-        <v>3.99961134672543</v>
+        <v>3.999611346725456</v>
       </c>
       <c r="H30" t="n">
-        <v>4.021973978873973</v>
+        <v>4.021973978873961</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2917,13 +2917,13 @@
         <v>180.333570877285</v>
       </c>
       <c r="S30" t="n">
-        <v>131.8202263797057</v>
+        <v>131.8202263797056</v>
       </c>
       <c r="T30" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U30" t="n">
-        <v>79.16168051490371</v>
+        <v>79.16168051490372</v>
       </c>
       <c r="V30" t="n">
         <v>93.51066719152016</v>
@@ -2935,7 +2935,7 @@
         <v>419.8627394453875</v>
       </c>
       <c r="Y30" t="n">
-        <v>251.9832086481073</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="31">
@@ -2975,7 +2975,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>9.483546242607703</v>
+        <v>10.3217920922054</v>
       </c>
       <c r="M31" t="n">
         <v>102.3923982877958</v>
@@ -2987,16 +2987,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P31" t="n">
-        <v>291.4220612627038</v>
+        <v>291.4220612627037</v>
       </c>
       <c r="Q31" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R31" t="n">
-        <v>377.7099312598395</v>
+        <v>377.7099312598396</v>
       </c>
       <c r="S31" t="n">
-        <v>30.56285675203577</v>
+        <v>29.72461090243842</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -3042,7 +3042,7 @@
         <v>81.3744577141519</v>
       </c>
       <c r="H32" t="n">
-        <v>72.84688483418068</v>
+        <v>73.30747219949504</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -3072,7 +3072,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>0.4605873653139497</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>142.3350019731772</v>
@@ -3103,19 +3103,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>237.1483725282995</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C33" t="n">
-        <v>361.0999124455193</v>
+        <v>213.6917283274922</v>
       </c>
       <c r="D33" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E33" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F33" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G33" t="n">
         <v>3.99961134672543</v>
@@ -3166,7 +3166,7 @@
         <v>93.51066719152016</v>
       </c>
       <c r="W33" t="n">
-        <v>432.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X33" t="n">
         <v>98.86273944538755</v>
@@ -3343,13 +3343,13 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C36" t="n">
-        <v>40.09991244551929</v>
+        <v>213.6917283274922</v>
       </c>
       <c r="D36" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E36" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F36" t="n">
         <v>339.6362423378769</v>
@@ -3385,22 +3385,22 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>501.333570877285</v>
+        <v>180.333570877285</v>
       </c>
       <c r="S36" t="n">
         <v>131.8202263797057</v>
       </c>
       <c r="T36" t="n">
-        <v>402.3753501231742</v>
+        <v>81.3753501231742</v>
       </c>
       <c r="U36" t="n">
         <v>79.16168051490371</v>
       </c>
       <c r="V36" t="n">
-        <v>188.4739349641459</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W36" t="n">
         <v>111.3731429098285</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>0.4605873653139497</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>142.3350019731772</v>
+        <v>142.7955893384911</v>
       </c>
       <c r="T38" t="n">
         <v>259.6218731858503</v>
@@ -3589,13 +3589,13 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F39" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G39" t="n">
         <v>3.999611346725456</v>
       </c>
       <c r="H39" t="n">
-        <v>325.021973978874</v>
+        <v>4.021973978873961</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -3634,7 +3634,7 @@
         <v>81.3753501231742</v>
       </c>
       <c r="U39" t="n">
-        <v>79.16168051490372</v>
+        <v>252.7534963968768</v>
       </c>
       <c r="V39" t="n">
         <v>93.51066719152016</v>
@@ -3643,7 +3643,7 @@
         <v>111.3731429098285</v>
       </c>
       <c r="X39" t="n">
-        <v>272.4545553273606</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y39" t="n">
         <v>78.39139276613435</v>
@@ -3750,10 +3750,10 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G41" t="n">
-        <v>81.3744577141519</v>
+        <v>81.37445771415189</v>
       </c>
       <c r="H41" t="n">
-        <v>73.30747219949504</v>
+        <v>72.84688483418068</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3783,7 +3783,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>0.4605873653139497</v>
       </c>
       <c r="S41" t="n">
         <v>142.3350019731772</v>
@@ -3814,25 +3814,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>384.5565566463266</v>
+        <v>237.1483725282997</v>
       </c>
       <c r="C42" t="n">
         <v>40.09991244551929</v>
       </c>
       <c r="D42" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E42" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F42" t="n">
         <v>18.63624233787687</v>
       </c>
       <c r="G42" t="n">
-        <v>3.99961134672543</v>
+        <v>3.999611346725456</v>
       </c>
       <c r="H42" t="n">
-        <v>4.021973978873973</v>
+        <v>4.021973978873961</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -3865,22 +3865,22 @@
         <v>180.333570877285</v>
       </c>
       <c r="S42" t="n">
-        <v>131.8202263797057</v>
+        <v>131.8202263797056</v>
       </c>
       <c r="T42" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U42" t="n">
-        <v>79.16168051490371</v>
+        <v>79.16168051490372</v>
       </c>
       <c r="V42" t="n">
-        <v>267.1024830734933</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W42" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X42" t="n">
-        <v>98.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y42" t="n">
         <v>78.39139276613435</v>
@@ -3923,28 +3923,28 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>10.32179209220538</v>
+        <v>10.3217920922054</v>
       </c>
       <c r="M43" t="n">
         <v>102.3923982877958</v>
       </c>
       <c r="N43" t="n">
-        <v>154.4197474548741</v>
+        <v>155.2579933044718</v>
       </c>
       <c r="O43" t="n">
         <v>231.765039488851</v>
       </c>
       <c r="P43" t="n">
-        <v>291.4220612627038</v>
+        <v>291.4220612627037</v>
       </c>
       <c r="Q43" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R43" t="n">
-        <v>377.7099312598395</v>
+        <v>377.7099312598396</v>
       </c>
       <c r="S43" t="n">
-        <v>30.56285675203577</v>
+        <v>29.72461090243842</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -3987,13 +3987,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G44" t="n">
-        <v>81.37445771415189</v>
+        <v>81.3744577141519</v>
       </c>
       <c r="H44" t="n">
         <v>72.84688483418068</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>0.4605873653143577</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4020,7 +4020,7 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0.4605873653139497</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>142.3350019731772</v>
@@ -4051,25 +4051,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>63.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C45" t="n">
-        <v>213.6917283274924</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D45" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E45" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F45" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G45" t="n">
-        <v>3.999611346725456</v>
+        <v>3.99961134672543</v>
       </c>
       <c r="H45" t="n">
-        <v>4.021973978873961</v>
+        <v>4.021973978873973</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -4102,13 +4102,13 @@
         <v>180.333570877285</v>
       </c>
       <c r="S45" t="n">
-        <v>131.8202263797056</v>
+        <v>131.8202263797057</v>
       </c>
       <c r="T45" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U45" t="n">
-        <v>79.16168051490372</v>
+        <v>79.16168051490371</v>
       </c>
       <c r="V45" t="n">
         <v>93.51066719152016</v>
@@ -4117,10 +4117,10 @@
         <v>111.3731429098285</v>
       </c>
       <c r="X45" t="n">
-        <v>98.86273944538755</v>
+        <v>272.4545553273606</v>
       </c>
       <c r="Y45" t="n">
-        <v>78.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="46">
@@ -4160,7 +4160,7 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>10.3217920922054</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M46" t="n">
         <v>102.3923982877958</v>
@@ -4172,16 +4172,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P46" t="n">
-        <v>291.4220612627037</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q46" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R46" t="n">
-        <v>377.7099312598396</v>
+        <v>377.7099312598395</v>
       </c>
       <c r="S46" t="n">
-        <v>29.72461090243842</v>
+        <v>29.72461090243831</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -4297,76 +4297,76 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>108.731003807232</v>
+        <v>106.7884999460195</v>
       </c>
       <c r="C2" t="n">
-        <v>58.7566823496624</v>
+        <v>56.81417848844992</v>
       </c>
       <c r="D2" t="n">
-        <v>48.31309069324847</v>
+        <v>46.37058683203599</v>
       </c>
       <c r="E2" t="n">
-        <v>43.90572745398721</v>
+        <v>41.96322359277473</v>
       </c>
       <c r="F2" t="n">
-        <v>38.96670855700554</v>
+        <v>37.02420469579306</v>
       </c>
       <c r="G2" t="n">
-        <v>35.58557518755106</v>
+        <v>33.64713203391685</v>
       </c>
       <c r="H2" t="n">
-        <v>31.736856432148</v>
+        <v>29.84</v>
       </c>
       <c r="I2" t="n">
-        <v>29.92</v>
+        <v>29.84</v>
       </c>
       <c r="J2" t="n">
-        <v>385.22</v>
+        <v>29.93969029977264</v>
       </c>
       <c r="K2" t="n">
-        <v>755.4799999999999</v>
+        <v>399.2096902997726</v>
       </c>
       <c r="L2" t="n">
-        <v>1125.74</v>
+        <v>694.7957936111288</v>
       </c>
       <c r="M2" t="n">
-        <v>1125.74</v>
+        <v>1064.065793611129</v>
       </c>
       <c r="N2" t="n">
-        <v>1125.74</v>
+        <v>1064.065793611129</v>
       </c>
       <c r="O2" t="n">
-        <v>1125.74</v>
+        <v>1433.335793611129</v>
       </c>
       <c r="P2" t="n">
-        <v>1496</v>
+        <v>1492</v>
       </c>
       <c r="Q2" t="n">
-        <v>1496</v>
+        <v>1492</v>
       </c>
       <c r="R2" t="n">
-        <v>1496</v>
+        <v>1492</v>
       </c>
       <c r="S2" t="n">
-        <v>1409.632174038565</v>
+        <v>1405.724707412506</v>
       </c>
       <c r="T2" t="n">
-        <v>1222.884106610596</v>
+        <v>1218.994415731961</v>
       </c>
       <c r="U2" t="n">
-        <v>971.1785586019998</v>
+        <v>967.2891925799706</v>
       </c>
       <c r="V2" t="n">
-        <v>739.0058069183393</v>
+        <v>735.1164408963101</v>
       </c>
       <c r="W2" t="n">
-        <v>498.2245180486953</v>
+        <v>494.3351520266661</v>
       </c>
       <c r="X2" t="n">
-        <v>304.0004438460006</v>
+        <v>300.1110778239714</v>
       </c>
       <c r="Y2" t="n">
-        <v>191.5585926512467</v>
+        <v>187.6692266292175</v>
       </c>
     </row>
     <row r="3">
@@ -4376,76 +4376,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>719.1203429896864</v>
+        <v>920.9501624906263</v>
       </c>
       <c r="C3" t="n">
-        <v>719.1203429896864</v>
+        <v>920.9501624906263</v>
       </c>
       <c r="D3" t="n">
-        <v>719.1203429896864</v>
+        <v>920.9501624906263</v>
       </c>
       <c r="E3" t="n">
-        <v>372.9869114524009</v>
+        <v>574.8167309533409</v>
       </c>
       <c r="F3" t="n">
-        <v>29.92</v>
+        <v>574.8167309533409</v>
       </c>
       <c r="G3" t="n">
-        <v>29.92</v>
+        <v>574.8167309533409</v>
       </c>
       <c r="H3" t="n">
-        <v>29.92</v>
+        <v>241.454702729969</v>
       </c>
       <c r="I3" t="n">
-        <v>29.92</v>
+        <v>29.84</v>
       </c>
       <c r="J3" t="n">
-        <v>174.3973709300159</v>
+        <v>170.7984703728021</v>
       </c>
       <c r="K3" t="n">
-        <v>398.6635894772295</v>
+        <v>395.4085458068081</v>
       </c>
       <c r="L3" t="n">
-        <v>717.174568996958</v>
+        <v>714.3818833454045</v>
       </c>
       <c r="M3" t="n">
-        <v>858.2892107398172</v>
+        <v>856.0360750882637</v>
       </c>
       <c r="N3" t="n">
-        <v>1048.06018421531</v>
+        <v>1046.360878846775</v>
       </c>
       <c r="O3" t="n">
-        <v>1338.780579861293</v>
+        <v>1337.587921002192</v>
       </c>
       <c r="P3" t="n">
-        <v>1492.786030368536</v>
+        <v>1492.000000000001</v>
       </c>
       <c r="Q3" t="n">
-        <v>1346.247111942856</v>
+        <v>1345.738421006377</v>
       </c>
       <c r="R3" t="n">
-        <v>1211.245105910912</v>
+        <v>1056.158209906665</v>
       </c>
       <c r="S3" t="n">
-        <v>1148.125094511552</v>
+        <v>993.0785549014354</v>
       </c>
       <c r="T3" t="n">
-        <v>1131.816638378404</v>
+        <v>988.568681516106</v>
       </c>
       <c r="U3" t="n">
-        <v>1131.618733532017</v>
+        <v>988.3709196085417</v>
       </c>
       <c r="V3" t="n">
-        <v>1116.961493944623</v>
+        <v>973.7136800211476</v>
       </c>
       <c r="W3" t="n">
-        <v>739.1837161668456</v>
+        <v>941.0135356677855</v>
       </c>
       <c r="X3" t="n">
-        <v>719.1203429896864</v>
+        <v>920.9501624906263</v>
       </c>
       <c r="Y3" t="n">
-        <v>719.1203429896864</v>
+        <v>920.9501624906263</v>
       </c>
     </row>
     <row r="4">
@@ -4455,76 +4455,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>483.4580055872682</v>
+        <v>637.1534903846377</v>
       </c>
       <c r="C4" t="n">
-        <v>483.4580055872682</v>
+        <v>705.1361798283964</v>
       </c>
       <c r="D4" t="n">
-        <v>483.4580055872682</v>
+        <v>818.4553239533965</v>
       </c>
       <c r="E4" t="n">
-        <v>483.4580055872682</v>
+        <v>936.2842281648095</v>
       </c>
       <c r="F4" t="n">
-        <v>483.4580055872682</v>
+        <v>1060.645200756745</v>
       </c>
       <c r="G4" t="n">
-        <v>483.4580055872682</v>
+        <v>1214.235646971499</v>
       </c>
       <c r="H4" t="n">
-        <v>654.5935815663379</v>
+        <v>1385.387095409585</v>
       </c>
       <c r="I4" t="n">
-        <v>881.2025562401257</v>
+        <v>1385.387095409585</v>
       </c>
       <c r="J4" t="n">
-        <v>1251.462556240126</v>
+        <v>1385.387095409585</v>
       </c>
       <c r="K4" t="n">
-        <v>1382.983127881912</v>
+        <v>1385.387095409585</v>
       </c>
       <c r="L4" t="n">
-        <v>1386.743548464727</v>
+        <v>1385.387095409585</v>
       </c>
       <c r="M4" t="n">
-        <v>1294.017231267251</v>
+        <v>1292.946305617309</v>
       </c>
       <c r="N4" t="n">
-        <v>1149.534310393385</v>
+        <v>1148.742122945132</v>
       </c>
       <c r="O4" t="n">
-        <v>932.9209073660642</v>
+        <v>932.3861797621563</v>
       </c>
       <c r="P4" t="n">
-        <v>665.0402361121327</v>
+        <v>664.7258098826245</v>
       </c>
       <c r="Q4" t="n">
-        <v>351.4672397226398</v>
+        <v>351.3053387456568</v>
       </c>
       <c r="R4" t="n">
-        <v>29.92</v>
+        <v>29.84</v>
       </c>
       <c r="S4" t="n">
-        <v>70.34367574991084</v>
+        <v>29.84</v>
       </c>
       <c r="T4" t="n">
-        <v>259.1973975316665</v>
+        <v>218.7013496506081</v>
       </c>
       <c r="U4" t="n">
-        <v>259.1973975316665</v>
+        <v>465.2625721249603</v>
       </c>
       <c r="V4" t="n">
-        <v>259.1973975316665</v>
+        <v>465.2625721249603</v>
       </c>
       <c r="W4" t="n">
-        <v>259.1973975316665</v>
+        <v>637.1534903846377</v>
       </c>
       <c r="X4" t="n">
-        <v>371.7006679209761</v>
+        <v>637.1534903846377</v>
       </c>
       <c r="Y4" t="n">
-        <v>371.7006679209761</v>
+        <v>637.1534903846377</v>
       </c>
     </row>
     <row r="5">
@@ -4534,49 +4534,49 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>108.731003807232</v>
+        <v>106.8684999460195</v>
       </c>
       <c r="C5" t="n">
-        <v>58.7566823496624</v>
+        <v>56.89417848844992</v>
       </c>
       <c r="D5" t="n">
-        <v>48.31309069324847</v>
+        <v>46.450586832036</v>
       </c>
       <c r="E5" t="n">
-        <v>43.90572745398721</v>
+        <v>42.04322359277474</v>
       </c>
       <c r="F5" t="n">
-        <v>38.96670855700554</v>
+        <v>37.10420469579307</v>
       </c>
       <c r="G5" t="n">
-        <v>35.58557518755106</v>
+        <v>33.72713203391686</v>
       </c>
       <c r="H5" t="n">
-        <v>31.736856432148</v>
+        <v>29.92</v>
       </c>
       <c r="I5" t="n">
         <v>29.92</v>
       </c>
       <c r="J5" t="n">
-        <v>29.92</v>
+        <v>30.01969029977264</v>
       </c>
       <c r="K5" t="n">
-        <v>400.18</v>
+        <v>400.2796902997726</v>
       </c>
       <c r="L5" t="n">
-        <v>770.4399999999999</v>
+        <v>770.5396902997726</v>
       </c>
       <c r="M5" t="n">
-        <v>1140.7</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="N5" t="n">
-        <v>1437.908108133742</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="O5" t="n">
-        <v>1437.908108133742</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="P5" t="n">
-        <v>1496</v>
+        <v>1125.74</v>
       </c>
       <c r="Q5" t="n">
         <v>1496</v>
@@ -4585,25 +4585,25 @@
         <v>1496</v>
       </c>
       <c r="S5" t="n">
-        <v>1409.632174038565</v>
+        <v>1407.751569573322</v>
       </c>
       <c r="T5" t="n">
-        <v>1222.884106610596</v>
+        <v>1221.021277892777</v>
       </c>
       <c r="U5" t="n">
-        <v>971.1785586019998</v>
+        <v>969.3160547407873</v>
       </c>
       <c r="V5" t="n">
-        <v>739.0058069183393</v>
+        <v>737.1433030571268</v>
       </c>
       <c r="W5" t="n">
-        <v>498.2245180486953</v>
+        <v>496.3620141874828</v>
       </c>
       <c r="X5" t="n">
-        <v>304.0004438460006</v>
+        <v>302.1379399847881</v>
       </c>
       <c r="Y5" t="n">
-        <v>191.5585926512467</v>
+        <v>189.6960887900342</v>
       </c>
     </row>
     <row r="6">
@@ -4613,10 +4613,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>171.4892686263505</v>
+        <v>29.92</v>
       </c>
       <c r="C6" t="n">
-        <v>171.4892686263505</v>
+        <v>29.92</v>
       </c>
       <c r="D6" t="n">
         <v>29.92</v>
@@ -4637,52 +4637,52 @@
         <v>29.92</v>
       </c>
       <c r="J6" t="n">
-        <v>174.3973709300159</v>
+        <v>174.5985557413367</v>
       </c>
       <c r="K6" t="n">
-        <v>398.6635894772295</v>
+        <v>399.2086311753428</v>
       </c>
       <c r="L6" t="n">
-        <v>717.174568996958</v>
+        <v>718.1819687139391</v>
       </c>
       <c r="M6" t="n">
-        <v>858.2892107398172</v>
+        <v>859.8361604567983</v>
       </c>
       <c r="N6" t="n">
-        <v>1048.06018421531</v>
+        <v>1050.16096421531</v>
       </c>
       <c r="O6" t="n">
-        <v>1338.780579861293</v>
+        <v>1341.388006370727</v>
       </c>
       <c r="P6" t="n">
-        <v>1492.786030368536</v>
+        <v>1495.800085368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1492.786030368536</v>
+        <v>1349.538506374912</v>
       </c>
       <c r="R6" t="n">
-        <v>1357.784024336592</v>
+        <v>1214.671396474091</v>
       </c>
       <c r="S6" t="n">
-        <v>980.0062465588139</v>
+        <v>1151.591741468861</v>
       </c>
       <c r="T6" t="n">
-        <v>602.2284687810361</v>
+        <v>1147.081868083532</v>
       </c>
       <c r="U6" t="n">
-        <v>602.0305639346496</v>
+        <v>1146.884106175968</v>
       </c>
       <c r="V6" t="n">
-        <v>224.2527861568718</v>
+        <v>769.1063283981898</v>
       </c>
       <c r="W6" t="n">
-        <v>191.5526418035097</v>
+        <v>736.4061840448277</v>
       </c>
       <c r="X6" t="n">
-        <v>171.4892686263505</v>
+        <v>358.6284062670499</v>
       </c>
       <c r="Y6" t="n">
-        <v>171.4892686263505</v>
+        <v>29.92</v>
       </c>
     </row>
     <row r="7">
@@ -4692,52 +4692,52 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>212.0404404070027</v>
+        <v>141.6773376662921</v>
       </c>
       <c r="C7" t="n">
-        <v>212.0404404070027</v>
+        <v>267.679343484728</v>
       </c>
       <c r="D7" t="n">
-        <v>212.0404404070027</v>
+        <v>380.998487609728</v>
       </c>
       <c r="E7" t="n">
-        <v>329.8693446184157</v>
+        <v>498.8273918211411</v>
       </c>
       <c r="F7" t="n">
-        <v>329.8693446184157</v>
+        <v>623.1883644130766</v>
       </c>
       <c r="G7" t="n">
-        <v>483.4580055872682</v>
+        <v>776.7788106278307</v>
       </c>
       <c r="H7" t="n">
-        <v>654.5935815663379</v>
+        <v>947.9302590659167</v>
       </c>
       <c r="I7" t="n">
-        <v>881.2025562401257</v>
+        <v>1174.592920952819</v>
       </c>
       <c r="J7" t="n">
-        <v>1251.462556240126</v>
+        <v>1253.739110653045</v>
       </c>
       <c r="K7" t="n">
-        <v>1382.983127881912</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="L7" t="n">
-        <v>1386.743548464727</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="M7" t="n">
-        <v>1294.017231267251</v>
+        <v>1293.026305617309</v>
       </c>
       <c r="N7" t="n">
-        <v>1149.534310393385</v>
+        <v>1148.822122945132</v>
       </c>
       <c r="O7" t="n">
-        <v>932.9209073660642</v>
+        <v>932.4661797621563</v>
       </c>
       <c r="P7" t="n">
-        <v>665.0402361121327</v>
+        <v>664.8058098826245</v>
       </c>
       <c r="Q7" t="n">
-        <v>351.4672397226398</v>
+        <v>351.3853387456568</v>
       </c>
       <c r="R7" t="n">
         <v>29.92</v>
@@ -4749,19 +4749,19 @@
         <v>29.92</v>
       </c>
       <c r="U7" t="n">
-        <v>61.00964938280916</v>
+        <v>29.92</v>
       </c>
       <c r="V7" t="n">
-        <v>61.00964938280916</v>
+        <v>29.92</v>
       </c>
       <c r="W7" t="n">
-        <v>61.00964938280916</v>
+        <v>29.92</v>
       </c>
       <c r="X7" t="n">
-        <v>212.0404404070027</v>
+        <v>29.92</v>
       </c>
       <c r="Y7" t="n">
-        <v>212.0404404070027</v>
+        <v>29.92</v>
       </c>
     </row>
     <row r="8">
@@ -4789,7 +4789,7 @@
         <v>35.70026987310013</v>
       </c>
       <c r="H8" t="n">
-        <v>31.89313783918327</v>
+        <v>29.92</v>
       </c>
       <c r="I8" t="n">
         <v>29.92</v>
@@ -4798,19 +4798,19 @@
         <v>30.01969029977264</v>
       </c>
       <c r="K8" t="n">
-        <v>385.2200000000001</v>
+        <v>400.2796902997726</v>
       </c>
       <c r="L8" t="n">
-        <v>755.48</v>
+        <v>770.5396902997726</v>
       </c>
       <c r="M8" t="n">
-        <v>1125.74</v>
+        <v>1140.799690299772</v>
       </c>
       <c r="N8" t="n">
-        <v>1125.74</v>
+        <v>1437.335793611129</v>
       </c>
       <c r="O8" t="n">
-        <v>1125.74</v>
+        <v>1437.335793611129</v>
       </c>
       <c r="P8" t="n">
         <v>1496</v>
@@ -4850,22 +4850,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>260.1566108800898</v>
+        <v>1079.463349058052</v>
       </c>
       <c r="C9" t="n">
-        <v>29.92</v>
+        <v>1079.463349058052</v>
       </c>
       <c r="D9" t="n">
-        <v>29.92</v>
+        <v>1079.463349058052</v>
       </c>
       <c r="E9" t="n">
-        <v>29.92</v>
+        <v>733.3299175207667</v>
       </c>
       <c r="F9" t="n">
-        <v>29.92</v>
+        <v>390.2630060683658</v>
       </c>
       <c r="G9" t="n">
-        <v>29.92</v>
+        <v>61.45695687117785</v>
       </c>
       <c r="H9" t="n">
         <v>29.92</v>
@@ -4895,31 +4895,31 @@
         <v>1495.800085368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1495.800085368536</v>
+        <v>1349.538506374912</v>
       </c>
       <c r="R9" t="n">
-        <v>1118.022307590758</v>
+        <v>1214.671396474091</v>
       </c>
       <c r="S9" t="n">
-        <v>1054.942652585528</v>
+        <v>1151.591741468861</v>
       </c>
       <c r="T9" t="n">
-        <v>1050.432779200199</v>
+        <v>1147.081868083532</v>
       </c>
       <c r="U9" t="n">
-        <v>672.6550014224208</v>
+        <v>1146.884106175968</v>
       </c>
       <c r="V9" t="n">
-        <v>657.9977618350267</v>
+        <v>1132.226866588574</v>
       </c>
       <c r="W9" t="n">
-        <v>280.2199840572489</v>
+        <v>1099.526722235211</v>
       </c>
       <c r="X9" t="n">
-        <v>260.1566108800898</v>
+        <v>1079.463349058052</v>
       </c>
       <c r="Y9" t="n">
-        <v>260.1566108800898</v>
+        <v>1079.463349058052</v>
       </c>
     </row>
     <row r="10">
@@ -4929,28 +4929,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>566.1042281648096</v>
+        <v>910.8149596824239</v>
       </c>
       <c r="C10" t="n">
-        <v>566.1042281648096</v>
+        <v>910.8149596824239</v>
       </c>
       <c r="D10" t="n">
-        <v>566.1042281648096</v>
+        <v>1024.134103807424</v>
       </c>
       <c r="E10" t="n">
-        <v>566.1042281648096</v>
+        <v>1024.134103807424</v>
       </c>
       <c r="F10" t="n">
-        <v>690.465200756745</v>
+        <v>1024.134103807424</v>
       </c>
       <c r="G10" t="n">
-        <v>844.0556469714992</v>
+        <v>1024.134103807424</v>
       </c>
       <c r="H10" t="n">
-        <v>1015.207095409585</v>
+        <v>1024.134103807424</v>
       </c>
       <c r="I10" t="n">
-        <v>1015.207095409585</v>
+        <v>1024.134103807424</v>
       </c>
       <c r="J10" t="n">
         <v>1385.467095409585</v>
@@ -4980,25 +4980,25 @@
         <v>29.92</v>
       </c>
       <c r="S10" t="n">
-        <v>29.92</v>
+        <v>70.37478771712392</v>
       </c>
       <c r="T10" t="n">
-        <v>218.7813496506081</v>
+        <v>70.37478771712392</v>
       </c>
       <c r="U10" t="n">
-        <v>218.7813496506081</v>
+        <v>316.9360101914762</v>
       </c>
       <c r="V10" t="n">
-        <v>342.9375898194852</v>
+        <v>515.7574030774222</v>
       </c>
       <c r="W10" t="n">
-        <v>342.9375898194852</v>
+        <v>687.6483213370996</v>
       </c>
       <c r="X10" t="n">
-        <v>342.9375898194852</v>
+        <v>687.6483213370996</v>
       </c>
       <c r="Y10" t="n">
-        <v>454.3468904985174</v>
+        <v>799.0576220161319</v>
       </c>
     </row>
     <row r="11">
@@ -5008,22 +5008,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>597.1205880922942</v>
+        <v>597.1205880922939</v>
       </c>
       <c r="C11" t="n">
-        <v>467.3482868367447</v>
+        <v>467.3482868367445</v>
       </c>
       <c r="D11" t="n">
-        <v>377.106715382351</v>
+        <v>377.1067153823507</v>
       </c>
       <c r="E11" t="n">
-        <v>292.9013723451099</v>
+        <v>292.9013723451097</v>
       </c>
       <c r="F11" t="n">
-        <v>208.1643736501484</v>
+        <v>208.1643736501482</v>
       </c>
       <c r="G11" t="n">
-        <v>125.9679517166617</v>
+        <v>125.9679517166614</v>
       </c>
       <c r="H11" t="n">
         <v>51.92</v>
@@ -5032,22 +5032,22 @@
         <v>51.92</v>
       </c>
       <c r="J11" t="n">
-        <v>559.4285273090126</v>
+        <v>133.4268380887174</v>
       </c>
       <c r="K11" t="n">
-        <v>1201.938527309012</v>
+        <v>775.9368380887173</v>
       </c>
       <c r="L11" t="n">
-        <v>1844.448527309012</v>
+        <v>1418.446838088717</v>
       </c>
       <c r="M11" t="n">
-        <v>1844.448527309012</v>
+        <v>1595.767892278425</v>
       </c>
       <c r="N11" t="n">
-        <v>1844.448527309012</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O11" t="n">
-        <v>2005.578628691967</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P11" t="n">
         <v>2596</v>
@@ -5068,16 +5068,16 @@
         <v>1858.558041876961</v>
       </c>
       <c r="V11" t="n">
-        <v>1546.587310395321</v>
+        <v>1546.58731039532</v>
       </c>
       <c r="W11" t="n">
         <v>1226.008041727697</v>
       </c>
       <c r="X11" t="n">
-        <v>951.9859877270223</v>
+        <v>951.9859877270221</v>
       </c>
       <c r="Y11" t="n">
-        <v>759.7461567342887</v>
+        <v>759.7461567342884</v>
       </c>
     </row>
     <row r="12">
@@ -5087,22 +5087,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1141.180125483445</v>
+        <v>264.3753454557946</v>
       </c>
       <c r="C12" t="n">
-        <v>776.43273917484</v>
+        <v>223.8703833896135</v>
       </c>
       <c r="D12" t="n">
-        <v>749.2229544296858</v>
+        <v>196.6605986444593</v>
       </c>
       <c r="E12" t="n">
-        <v>403.0895228924003</v>
+        <v>174.7695913495981</v>
       </c>
       <c r="F12" t="n">
-        <v>384.2650356824237</v>
+        <v>155.9451041396215</v>
       </c>
       <c r="G12" t="n">
-        <v>55.98259997866058</v>
+        <v>55.98259997866057</v>
       </c>
       <c r="H12" t="n">
         <v>51.92</v>
@@ -5132,31 +5132,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q12" t="n">
-        <v>2244.187340368535</v>
+        <v>2164.764564500508</v>
       </c>
       <c r="R12" t="n">
-        <v>2062.032218270268</v>
+        <v>1658.367018159816</v>
       </c>
       <c r="S12" t="n">
-        <v>1928.880474452383</v>
+        <v>1200.972850099507</v>
       </c>
       <c r="T12" t="n">
-        <v>1846.683151095641</v>
+        <v>1118.775526742765</v>
       </c>
       <c r="U12" t="n">
-        <v>1766.721857646244</v>
+        <v>1038.814233293368</v>
       </c>
       <c r="V12" t="n">
-        <v>1496.92136969322</v>
+        <v>944.3590139079937</v>
       </c>
       <c r="W12" t="n">
-        <v>1384.423245541878</v>
+        <v>831.8608897566518</v>
       </c>
       <c r="X12" t="n">
-        <v>1284.561892566739</v>
+        <v>407.7571125390886</v>
       </c>
       <c r="Y12" t="n">
-        <v>1205.378667550442</v>
+        <v>328.5738875227912</v>
       </c>
     </row>
     <row r="13">
@@ -5196,7 +5196,7 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L13" t="n">
-        <v>1609.501360385148</v>
+        <v>1608.654647405756</v>
       </c>
       <c r="M13" t="n">
         <v>1506.07469544798</v>
@@ -5211,7 +5211,7 @@
         <v>820.7766206439126</v>
       </c>
       <c r="Q13" t="n">
-        <v>464.3167555675508</v>
+        <v>464.3167555675509</v>
       </c>
       <c r="R13" t="n">
         <v>82.79157247680381</v>
@@ -5245,22 +5245,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>597.1205880922939</v>
+        <v>596.6553483293503</v>
       </c>
       <c r="C14" t="n">
-        <v>467.3482868367445</v>
+        <v>466.8830470738009</v>
       </c>
       <c r="D14" t="n">
-        <v>377.1067153823507</v>
+        <v>376.6414756194072</v>
       </c>
       <c r="E14" t="n">
-        <v>292.9013723451097</v>
+        <v>292.4361325821661</v>
       </c>
       <c r="F14" t="n">
-        <v>208.1643736501482</v>
+        <v>207.6991338872047</v>
       </c>
       <c r="G14" t="n">
-        <v>125.9679517166614</v>
+        <v>125.5027119537179</v>
       </c>
       <c r="H14" t="n">
         <v>51.92</v>
@@ -5272,49 +5272,49 @@
         <v>559.4285273090126</v>
       </c>
       <c r="K14" t="n">
-        <v>1201.938527309012</v>
+        <v>1009.32297330616</v>
       </c>
       <c r="L14" t="n">
-        <v>1844.448527309012</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="M14" t="n">
-        <v>1844.448527309012</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="N14" t="n">
-        <v>1844.448527309012</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="O14" t="n">
-        <v>2005.578628691967</v>
+        <v>1812.963074689115</v>
       </c>
       <c r="P14" t="n">
-        <v>2202.170635030587</v>
+        <v>2009.555081027735</v>
       </c>
       <c r="Q14" t="n">
         <v>2596</v>
       </c>
       <c r="R14" t="n">
-        <v>2596</v>
+        <v>2595.534760237057</v>
       </c>
       <c r="S14" t="n">
-        <v>2452.227270734164</v>
+        <v>2451.762030971221</v>
       </c>
       <c r="T14" t="n">
-        <v>2189.982954384821</v>
+        <v>2189.517714621877</v>
       </c>
       <c r="U14" t="n">
-        <v>1858.558041876961</v>
+        <v>1858.092802114017</v>
       </c>
       <c r="V14" t="n">
-        <v>1546.58731039532</v>
+        <v>1546.122070632377</v>
       </c>
       <c r="W14" t="n">
-        <v>1226.008041727697</v>
+        <v>1225.542801964753</v>
       </c>
       <c r="X14" t="n">
-        <v>951.9859877270221</v>
+        <v>951.5207479640785</v>
       </c>
       <c r="Y14" t="n">
-        <v>759.7461567342884</v>
+        <v>759.2809169713448</v>
       </c>
     </row>
     <row r="15">
@@ -5324,22 +5324,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>168.4528527561725</v>
+        <v>992.2829698086706</v>
       </c>
       <c r="C15" t="n">
-        <v>127.9478906899915</v>
+        <v>951.7780077424895</v>
       </c>
       <c r="D15" t="n">
-        <v>100.7381059448373</v>
+        <v>924.5682229973354</v>
       </c>
       <c r="E15" t="n">
-        <v>78.84709864997603</v>
+        <v>578.4347914600498</v>
       </c>
       <c r="F15" t="n">
-        <v>60.02261143999941</v>
+        <v>559.6103042500732</v>
       </c>
       <c r="G15" t="n">
-        <v>55.98259997866057</v>
+        <v>231.3278685463101</v>
       </c>
       <c r="H15" t="n">
         <v>51.92</v>
@@ -5378,22 +5378,22 @@
         <v>1928.880474452383</v>
       </c>
       <c r="T15" t="n">
-        <v>1846.683151095642</v>
+        <v>1846.683151095641</v>
       </c>
       <c r="U15" t="n">
-        <v>1591.376589078594</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V15" t="n">
-        <v>1496.92136969322</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W15" t="n">
-        <v>1060.180821299454</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X15" t="n">
-        <v>636.0770440818907</v>
+        <v>1135.664736891964</v>
       </c>
       <c r="Y15" t="n">
-        <v>556.8938190655933</v>
+        <v>1056.481511875667</v>
       </c>
     </row>
     <row r="16">
@@ -5445,13 +5445,13 @@
         <v>1114.295626111697</v>
       </c>
       <c r="P16" t="n">
-        <v>819.9299076645212</v>
+        <v>819.9299076645211</v>
       </c>
       <c r="Q16" t="n">
-        <v>463.4700425881596</v>
+        <v>463.4700425881595</v>
       </c>
       <c r="R16" t="n">
-        <v>81.94485949741255</v>
+        <v>81.94485949741244</v>
       </c>
       <c r="S16" t="n">
         <v>51.92</v>
@@ -5500,31 +5500,31 @@
         <v>125.9679517166617</v>
       </c>
       <c r="H17" t="n">
-        <v>51.92</v>
+        <v>52.3852397629438</v>
       </c>
       <c r="I17" t="n">
         <v>51.92</v>
       </c>
       <c r="J17" t="n">
-        <v>559.4285273090126</v>
+        <v>133.4268380887174</v>
       </c>
       <c r="K17" t="n">
-        <v>1201.938527309012</v>
+        <v>775.9368380887173</v>
       </c>
       <c r="L17" t="n">
-        <v>1417.990475851726</v>
+        <v>1418.446838088717</v>
       </c>
       <c r="M17" t="n">
-        <v>1417.990475851726</v>
+        <v>1595.767892278425</v>
       </c>
       <c r="N17" t="n">
-        <v>1417.990475851726</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O17" t="n">
-        <v>1579.120577234681</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P17" t="n">
-        <v>2009.555081027735</v>
+        <v>2596</v>
       </c>
       <c r="Q17" t="n">
         <v>2596</v>
@@ -5561,16 +5561,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1141.180125483445</v>
+        <v>1316.525394051095</v>
       </c>
       <c r="C18" t="n">
-        <v>776.43273917484</v>
+        <v>1100.675163417264</v>
       </c>
       <c r="D18" t="n">
-        <v>424.9805301872615</v>
+        <v>749.2229544296858</v>
       </c>
       <c r="E18" t="n">
-        <v>78.84709864997603</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F18" t="n">
         <v>60.0226114399994</v>
@@ -5719,49 +5719,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>597.1205880922942</v>
+        <v>597.1205880922939</v>
       </c>
       <c r="C20" t="n">
-        <v>467.3482868367447</v>
+        <v>467.3482868367445</v>
       </c>
       <c r="D20" t="n">
-        <v>377.106715382351</v>
+        <v>377.1067153823507</v>
       </c>
       <c r="E20" t="n">
-        <v>292.9013723451099</v>
+        <v>292.9013723451097</v>
       </c>
       <c r="F20" t="n">
-        <v>208.1643736501484</v>
+        <v>208.1643736501482</v>
       </c>
       <c r="G20" t="n">
-        <v>125.9679517166617</v>
+        <v>125.9679517166614</v>
       </c>
       <c r="H20" t="n">
-        <v>52.3852397629438</v>
+        <v>52.38523976294358</v>
       </c>
       <c r="I20" t="n">
         <v>51.92</v>
       </c>
       <c r="J20" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K20" t="n">
-        <v>310.7478922784251</v>
+        <v>1201.938527309012</v>
       </c>
       <c r="L20" t="n">
-        <v>953.2578922784251</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="M20" t="n">
-        <v>1595.767892278425</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="N20" t="n">
-        <v>2238.277892278425</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="O20" t="n">
-        <v>2399.40799366138</v>
+        <v>1812.963074689115</v>
       </c>
       <c r="P20" t="n">
-        <v>2596</v>
+        <v>2009.555081027735</v>
       </c>
       <c r="Q20" t="n">
         <v>2596</v>
@@ -5779,16 +5779,16 @@
         <v>1858.558041876961</v>
       </c>
       <c r="V20" t="n">
-        <v>1546.587310395321</v>
+        <v>1546.58731039532</v>
       </c>
       <c r="W20" t="n">
         <v>1226.008041727697</v>
       </c>
       <c r="X20" t="n">
-        <v>951.9859877270223</v>
+        <v>951.9859877270221</v>
       </c>
       <c r="Y20" t="n">
-        <v>759.7461567342887</v>
+        <v>759.7461567342884</v>
       </c>
     </row>
     <row r="21">
@@ -5798,76 +5798,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>844.5079366300615</v>
+        <v>1141.180125483445</v>
       </c>
       <c r="C21" t="n">
-        <v>479.7605503214561</v>
+        <v>776.43273917484</v>
       </c>
       <c r="D21" t="n">
-        <v>452.5507655763019</v>
+        <v>424.9805301872615</v>
       </c>
       <c r="E21" t="n">
-        <v>430.6597582814406</v>
+        <v>78.84709864997603</v>
       </c>
       <c r="F21" t="n">
-        <v>411.835271071464</v>
+        <v>60.02261143999941</v>
       </c>
       <c r="G21" t="n">
-        <v>407.7952596101252</v>
+        <v>55.98259997866057</v>
       </c>
       <c r="H21" t="n">
-        <v>403.7326596314647</v>
+        <v>51.92</v>
       </c>
       <c r="I21" t="n">
-        <v>403.7326596314647</v>
+        <v>51.92</v>
       </c>
       <c r="J21" t="n">
-        <v>596.8967549011032</v>
+        <v>245.0840952696386</v>
       </c>
       <c r="K21" t="n">
-        <v>904.3763400520904</v>
+        <v>552.5636804206258</v>
       </c>
       <c r="L21" t="n">
-        <v>1334.777960137857</v>
+        <v>982.9653005063919</v>
       </c>
       <c r="M21" t="n">
-        <v>1606.463701880716</v>
+        <v>1254.651042249251</v>
       </c>
       <c r="N21" t="n">
-        <v>1930.261603846775</v>
+        <v>1578.44894421531</v>
       </c>
       <c r="O21" t="n">
-        <v>2343.590454775776</v>
+        <v>1991.777795144312</v>
       </c>
       <c r="P21" t="n">
-        <v>2596</v>
+        <v>2244.187340368535</v>
       </c>
       <c r="Q21" t="n">
-        <v>2596</v>
+        <v>2244.187340368535</v>
       </c>
       <c r="R21" t="n">
-        <v>2413.844877901732</v>
+        <v>2062.032218270268</v>
       </c>
       <c r="S21" t="n">
-        <v>2280.693134083848</v>
+        <v>1928.880474452383</v>
       </c>
       <c r="T21" t="n">
-        <v>2198.495810727106</v>
+        <v>1846.683151095642</v>
       </c>
       <c r="U21" t="n">
-        <v>2118.534517277709</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V21" t="n">
-        <v>1699.836873649911</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W21" t="n">
-        <v>1587.338749498569</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X21" t="n">
-        <v>1163.234972281005</v>
+        <v>1459.907161134389</v>
       </c>
       <c r="Y21" t="n">
-        <v>908.7064786970581</v>
+        <v>1380.723936118092</v>
       </c>
     </row>
     <row r="22">
@@ -5907,25 +5907,25 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L22" t="n">
-        <v>1608.654647405756</v>
+        <v>1609.501360385148</v>
       </c>
       <c r="M22" t="n">
-        <v>1505.227982468588</v>
+        <v>1506.07469544798</v>
       </c>
       <c r="N22" t="n">
-        <v>1348.401726605486</v>
+        <v>1349.248439584877</v>
       </c>
       <c r="O22" t="n">
-        <v>1114.295626111697</v>
+        <v>1115.142339091088</v>
       </c>
       <c r="P22" t="n">
-        <v>819.9299076645211</v>
+        <v>820.7766206439126</v>
       </c>
       <c r="Q22" t="n">
-        <v>463.4700425881595</v>
+        <v>464.3167555675509</v>
       </c>
       <c r="R22" t="n">
-        <v>81.94485949741244</v>
+        <v>82.79157247680381</v>
       </c>
       <c r="S22" t="n">
         <v>51.92</v>
@@ -5956,22 +5956,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>597.1205880922939</v>
+        <v>596.6553483293503</v>
       </c>
       <c r="C23" t="n">
-        <v>467.3482868367445</v>
+        <v>466.8830470738009</v>
       </c>
       <c r="D23" t="n">
-        <v>377.1067153823507</v>
+        <v>376.6414756194072</v>
       </c>
       <c r="E23" t="n">
-        <v>292.9013723451097</v>
+        <v>292.4361325821661</v>
       </c>
       <c r="F23" t="n">
-        <v>208.1643736501482</v>
+        <v>207.6991338872047</v>
       </c>
       <c r="G23" t="n">
-        <v>125.9679517166614</v>
+        <v>125.5027119537179</v>
       </c>
       <c r="H23" t="n">
         <v>51.92</v>
@@ -5989,10 +5989,10 @@
         <v>1418.446838088717</v>
       </c>
       <c r="M23" t="n">
-        <v>1418.446838088717</v>
+        <v>1595.767892278425</v>
       </c>
       <c r="N23" t="n">
-        <v>2060.956838088718</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O23" t="n">
         <v>2399.40799366138</v>
@@ -6004,28 +6004,28 @@
         <v>2596</v>
       </c>
       <c r="R23" t="n">
-        <v>2596</v>
+        <v>2595.534760237057</v>
       </c>
       <c r="S23" t="n">
-        <v>2452.227270734164</v>
+        <v>2451.762030971221</v>
       </c>
       <c r="T23" t="n">
-        <v>2189.982954384821</v>
+        <v>2189.517714621877</v>
       </c>
       <c r="U23" t="n">
-        <v>1858.558041876961</v>
+        <v>1858.092802114017</v>
       </c>
       <c r="V23" t="n">
-        <v>1546.58731039532</v>
+        <v>1546.122070632377</v>
       </c>
       <c r="W23" t="n">
-        <v>1226.008041727697</v>
+        <v>1225.542801964753</v>
       </c>
       <c r="X23" t="n">
-        <v>951.9859877270221</v>
+        <v>951.5207479640785</v>
       </c>
       <c r="Y23" t="n">
-        <v>759.7461567342884</v>
+        <v>759.2809169713448</v>
       </c>
     </row>
     <row r="24">
@@ -6035,22 +6035,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>168.4528527561725</v>
+        <v>1141.180125483445</v>
       </c>
       <c r="C24" t="n">
-        <v>127.9478906899915</v>
+        <v>1100.675163417264</v>
       </c>
       <c r="D24" t="n">
-        <v>100.7381059448373</v>
+        <v>749.2229544296858</v>
       </c>
       <c r="E24" t="n">
-        <v>78.84709864997603</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F24" t="n">
-        <v>60.02261143999941</v>
+        <v>60.0226114399994</v>
       </c>
       <c r="G24" t="n">
-        <v>55.98259997866057</v>
+        <v>55.98259997866058</v>
       </c>
       <c r="H24" t="n">
         <v>51.92</v>
@@ -6089,22 +6089,22 @@
         <v>1928.880474452383</v>
       </c>
       <c r="T24" t="n">
-        <v>1846.683151095642</v>
+        <v>1846.683151095641</v>
       </c>
       <c r="U24" t="n">
-        <v>1442.479433403819</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V24" t="n">
-        <v>1023.781789776021</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W24" t="n">
-        <v>735.9383970570296</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X24" t="n">
-        <v>636.0770440818907</v>
+        <v>1459.907161134389</v>
       </c>
       <c r="Y24" t="n">
-        <v>556.8938190655933</v>
+        <v>1380.723936118091</v>
       </c>
     </row>
     <row r="25">
@@ -6156,13 +6156,13 @@
         <v>1114.295626111697</v>
       </c>
       <c r="P25" t="n">
-        <v>819.9299076645212</v>
+        <v>819.9299076645211</v>
       </c>
       <c r="Q25" t="n">
-        <v>463.4700425881596</v>
+        <v>463.4700425881595</v>
       </c>
       <c r="R25" t="n">
-        <v>81.94485949741255</v>
+        <v>81.94485949741244</v>
       </c>
       <c r="S25" t="n">
         <v>51.92</v>
@@ -6193,25 +6193,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>597.1205880922939</v>
+        <v>596.6553483293503</v>
       </c>
       <c r="C26" t="n">
-        <v>467.3482868367445</v>
+        <v>466.8830470738009</v>
       </c>
       <c r="D26" t="n">
-        <v>377.1067153823507</v>
+        <v>376.6414756194072</v>
       </c>
       <c r="E26" t="n">
-        <v>292.9013723451097</v>
+        <v>292.4361325821661</v>
       </c>
       <c r="F26" t="n">
-        <v>208.1643736501482</v>
+        <v>207.6991338872046</v>
       </c>
       <c r="G26" t="n">
-        <v>125.9679517166614</v>
+        <v>125.5027119537179</v>
       </c>
       <c r="H26" t="n">
-        <v>52.38523976294358</v>
+        <v>51.92</v>
       </c>
       <c r="I26" t="n">
         <v>51.92</v>
@@ -6220,16 +6220,16 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K26" t="n">
-        <v>775.9368380887173</v>
+        <v>307.5796384907274</v>
       </c>
       <c r="L26" t="n">
-        <v>1418.446838088717</v>
+        <v>523.631587033441</v>
       </c>
       <c r="M26" t="n">
-        <v>2060.956838088718</v>
+        <v>1114.38799366138</v>
       </c>
       <c r="N26" t="n">
-        <v>2238.277892278425</v>
+        <v>1756.89799366138</v>
       </c>
       <c r="O26" t="n">
         <v>2399.40799366138</v>
@@ -6241,28 +6241,28 @@
         <v>2596</v>
       </c>
       <c r="R26" t="n">
-        <v>2596</v>
+        <v>2595.534760237057</v>
       </c>
       <c r="S26" t="n">
-        <v>2452.227270734164</v>
+        <v>2451.762030971221</v>
       </c>
       <c r="T26" t="n">
-        <v>2189.982954384821</v>
+        <v>2189.517714621877</v>
       </c>
       <c r="U26" t="n">
-        <v>1858.558041876961</v>
+        <v>1858.092802114017</v>
       </c>
       <c r="V26" t="n">
-        <v>1546.58731039532</v>
+        <v>1546.122070632377</v>
       </c>
       <c r="W26" t="n">
-        <v>1226.008041727697</v>
+        <v>1225.542801964753</v>
       </c>
       <c r="X26" t="n">
-        <v>951.9859877270221</v>
+        <v>951.5207479640785</v>
       </c>
       <c r="Y26" t="n">
-        <v>759.7461567342884</v>
+        <v>759.2809169713448</v>
       </c>
     </row>
     <row r="27">
@@ -6272,25 +6272,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>362.0396347695416</v>
+        <v>1141.180125483445</v>
       </c>
       <c r="C27" t="n">
-        <v>321.5346727033605</v>
+        <v>776.43273917484</v>
       </c>
       <c r="D27" t="n">
-        <v>294.3248879582063</v>
+        <v>424.9805301872615</v>
       </c>
       <c r="E27" t="n">
-        <v>272.4338806633451</v>
+        <v>78.84709864997603</v>
       </c>
       <c r="F27" t="n">
-        <v>253.6093934533685</v>
+        <v>60.02261143999941</v>
       </c>
       <c r="G27" t="n">
-        <v>249.5693819920296</v>
+        <v>55.98259997866057</v>
       </c>
       <c r="H27" t="n">
-        <v>245.506782013369</v>
+        <v>51.92</v>
       </c>
       <c r="I27" t="n">
         <v>51.92</v>
@@ -6329,19 +6329,19 @@
         <v>1846.683151095642</v>
       </c>
       <c r="U27" t="n">
-        <v>1442.479433403819</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V27" t="n">
-        <v>1042.023303221741</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W27" t="n">
-        <v>929.5251790703988</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X27" t="n">
-        <v>829.6638260952599</v>
+        <v>1459.907161134389</v>
       </c>
       <c r="Y27" t="n">
-        <v>750.4806010789625</v>
+        <v>1380.723936118092</v>
       </c>
     </row>
     <row r="28">
@@ -6381,25 +6381,25 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L28" t="n">
-        <v>1609.501360385148</v>
+        <v>1608.654647405756</v>
       </c>
       <c r="M28" t="n">
-        <v>1506.07469544798</v>
+        <v>1505.227982468588</v>
       </c>
       <c r="N28" t="n">
-        <v>1349.248439584877</v>
+        <v>1348.401726605486</v>
       </c>
       <c r="O28" t="n">
-        <v>1115.142339091088</v>
+        <v>1114.295626111697</v>
       </c>
       <c r="P28" t="n">
-        <v>820.7766206439126</v>
+        <v>819.9299076645212</v>
       </c>
       <c r="Q28" t="n">
-        <v>464.3167555675509</v>
+        <v>463.4700425881596</v>
       </c>
       <c r="R28" t="n">
-        <v>82.79157247680381</v>
+        <v>81.94485949741255</v>
       </c>
       <c r="S28" t="n">
         <v>51.92</v>
@@ -6430,22 +6430,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922939</v>
       </c>
       <c r="C29" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367445</v>
       </c>
       <c r="D29" t="n">
-        <v>376.6414756194072</v>
+        <v>377.1067153823507</v>
       </c>
       <c r="E29" t="n">
-        <v>292.4361325821661</v>
+        <v>292.9013723451097</v>
       </c>
       <c r="F29" t="n">
-        <v>207.6991338872047</v>
+        <v>208.1643736501482</v>
       </c>
       <c r="G29" t="n">
-        <v>125.5027119537179</v>
+        <v>125.9679517166614</v>
       </c>
       <c r="H29" t="n">
         <v>51.92</v>
@@ -6457,49 +6457,49 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K29" t="n">
-        <v>307.5796384907274</v>
+        <v>775.9368380887173</v>
       </c>
       <c r="L29" t="n">
-        <v>523.631587033441</v>
+        <v>1418.446838088717</v>
       </c>
       <c r="M29" t="n">
-        <v>724.5350810277346</v>
+        <v>2060.956838088718</v>
       </c>
       <c r="N29" t="n">
-        <v>724.5350810277346</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O29" t="n">
-        <v>1367.045081027735</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P29" t="n">
-        <v>2009.555081027735</v>
+        <v>2596</v>
       </c>
       <c r="Q29" t="n">
         <v>2596</v>
       </c>
       <c r="R29" t="n">
-        <v>2595.534760237057</v>
+        <v>2596</v>
       </c>
       <c r="S29" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T29" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U29" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V29" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.58731039532</v>
       </c>
       <c r="W29" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X29" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270221</v>
       </c>
       <c r="Y29" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342884</v>
       </c>
     </row>
     <row r="30">
@@ -6509,22 +6509,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>816.937701241021</v>
+        <v>992.2829698086708</v>
       </c>
       <c r="C30" t="n">
-        <v>776.43273917484</v>
+        <v>627.5355835000655</v>
       </c>
       <c r="D30" t="n">
-        <v>749.2229544296858</v>
+        <v>600.3257987549114</v>
       </c>
       <c r="E30" t="n">
-        <v>403.0895228924003</v>
+        <v>254.1923672176259</v>
       </c>
       <c r="F30" t="n">
-        <v>60.0226114399994</v>
+        <v>60.02261143999941</v>
       </c>
       <c r="G30" t="n">
-        <v>55.98259997866058</v>
+        <v>55.98259997866057</v>
       </c>
       <c r="H30" t="n">
         <v>51.92</v>
@@ -6563,7 +6563,7 @@
         <v>1928.880474452383</v>
       </c>
       <c r="T30" t="n">
-        <v>1846.683151095641</v>
+        <v>1846.683151095642</v>
       </c>
       <c r="U30" t="n">
         <v>1766.721857646244</v>
@@ -6575,10 +6575,10 @@
         <v>1559.768514109528</v>
       </c>
       <c r="X30" t="n">
-        <v>1135.664736891964</v>
+        <v>1135.664736891965</v>
       </c>
       <c r="Y30" t="n">
-        <v>881.1362433080176</v>
+        <v>1056.481511875667</v>
       </c>
     </row>
     <row r="31">
@@ -6618,25 +6618,25 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L31" t="n">
-        <v>1609.501360385148</v>
+        <v>1608.654647405756</v>
       </c>
       <c r="M31" t="n">
-        <v>1506.07469544798</v>
+        <v>1505.227982468588</v>
       </c>
       <c r="N31" t="n">
-        <v>1349.248439584877</v>
+        <v>1348.401726605486</v>
       </c>
       <c r="O31" t="n">
-        <v>1115.142339091088</v>
+        <v>1114.295626111697</v>
       </c>
       <c r="P31" t="n">
-        <v>820.7766206439126</v>
+        <v>819.9299076645212</v>
       </c>
       <c r="Q31" t="n">
-        <v>464.3167555675508</v>
+        <v>463.4700425881596</v>
       </c>
       <c r="R31" t="n">
-        <v>82.79157247680381</v>
+        <v>81.94485949741255</v>
       </c>
       <c r="S31" t="n">
         <v>51.92</v>
@@ -6667,22 +6667,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922942</v>
       </c>
       <c r="C32" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367447</v>
       </c>
       <c r="D32" t="n">
-        <v>376.6414756194072</v>
+        <v>377.106715382351</v>
       </c>
       <c r="E32" t="n">
-        <v>292.4361325821661</v>
+        <v>292.9013723451099</v>
       </c>
       <c r="F32" t="n">
-        <v>207.6991338872047</v>
+        <v>208.1643736501484</v>
       </c>
       <c r="G32" t="n">
-        <v>125.5027119537179</v>
+        <v>125.9679517166617</v>
       </c>
       <c r="H32" t="n">
         <v>51.92</v>
@@ -6700,43 +6700,43 @@
         <v>1418.446838088717</v>
       </c>
       <c r="M32" t="n">
-        <v>1418.446838088717</v>
+        <v>2060.956838088718</v>
       </c>
       <c r="N32" t="n">
-        <v>1651.83297330616</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O32" t="n">
-        <v>1812.963074689115</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P32" t="n">
-        <v>2009.555081027735</v>
+        <v>2596</v>
       </c>
       <c r="Q32" t="n">
         <v>2596</v>
       </c>
       <c r="R32" t="n">
-        <v>2595.534760237057</v>
+        <v>2596</v>
       </c>
       <c r="S32" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T32" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U32" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V32" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.587310395321</v>
       </c>
       <c r="W32" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X32" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270223</v>
       </c>
       <c r="Y32" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342887</v>
       </c>
     </row>
     <row r="33">
@@ -6746,16 +6746,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>816.9377012410212</v>
+        <v>1316.525394051095</v>
       </c>
       <c r="C33" t="n">
-        <v>452.1903149324157</v>
+        <v>1100.675163417264</v>
       </c>
       <c r="D33" t="n">
-        <v>424.9805301872615</v>
+        <v>749.2229544296858</v>
       </c>
       <c r="E33" t="n">
-        <v>78.84709864997603</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F33" t="n">
         <v>60.0226114399994</v>
@@ -6809,13 +6809,13 @@
         <v>1672.26663826087</v>
       </c>
       <c r="W33" t="n">
-        <v>1235.526089867103</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X33" t="n">
-        <v>1135.664736891964</v>
+        <v>1459.907161134389</v>
       </c>
       <c r="Y33" t="n">
-        <v>1056.481511875667</v>
+        <v>1380.723936118091</v>
       </c>
     </row>
     <row r="34">
@@ -6931,19 +6931,19 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K35" t="n">
-        <v>775.9368380887173</v>
+        <v>366.8129733061596</v>
       </c>
       <c r="L35" t="n">
-        <v>1418.446838088717</v>
+        <v>1009.32297330616</v>
       </c>
       <c r="M35" t="n">
-        <v>1418.446838088717</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="N35" t="n">
-        <v>1418.446838088717</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="O35" t="n">
-        <v>1579.576939471672</v>
+        <v>1812.963074689115</v>
       </c>
       <c r="P35" t="n">
         <v>2009.555081027735</v>
@@ -6983,13 +6983,13 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>492.6952769985969</v>
+        <v>1316.525394051095</v>
       </c>
       <c r="C36" t="n">
-        <v>452.1903149324158</v>
+        <v>1100.675163417264</v>
       </c>
       <c r="D36" t="n">
-        <v>424.9805301872616</v>
+        <v>749.2229544296858</v>
       </c>
       <c r="E36" t="n">
         <v>403.0895228924003</v>
@@ -7028,31 +7028,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q36" t="n">
-        <v>2164.764564500508</v>
+        <v>2244.187340368535</v>
       </c>
       <c r="R36" t="n">
-        <v>1658.367018159816</v>
+        <v>2062.032218270268</v>
       </c>
       <c r="S36" t="n">
-        <v>1525.215274341931</v>
+        <v>1928.880474452383</v>
       </c>
       <c r="T36" t="n">
-        <v>1118.775526742765</v>
+        <v>1846.683151095641</v>
       </c>
       <c r="U36" t="n">
-        <v>1038.814233293368</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V36" t="n">
-        <v>848.4365212083717</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W36" t="n">
-        <v>735.9383970570298</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X36" t="n">
-        <v>636.0770440818908</v>
+        <v>1459.907161134389</v>
       </c>
       <c r="Y36" t="n">
-        <v>556.8938190655934</v>
+        <v>1380.723936118091</v>
       </c>
     </row>
     <row r="37">
@@ -7165,22 +7165,22 @@
         <v>51.92</v>
       </c>
       <c r="J38" t="n">
-        <v>559.4285273090126</v>
+        <v>133.4268380887174</v>
       </c>
       <c r="K38" t="n">
-        <v>733.5813277110226</v>
+        <v>775.9368380887173</v>
       </c>
       <c r="L38" t="n">
-        <v>949.6332762537361</v>
+        <v>1418.446838088717</v>
       </c>
       <c r="M38" t="n">
-        <v>1205.91497964478</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="N38" t="n">
-        <v>1205.91497964478</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="O38" t="n">
-        <v>1367.045081027735</v>
+        <v>1812.963074689115</v>
       </c>
       <c r="P38" t="n">
         <v>2009.555081027735</v>
@@ -7189,7 +7189,7 @@
         <v>2596</v>
       </c>
       <c r="R38" t="n">
-        <v>2595.534760237057</v>
+        <v>2596</v>
       </c>
       <c r="S38" t="n">
         <v>2451.762030971221</v>
@@ -7232,10 +7232,10 @@
         <v>403.0895228924003</v>
       </c>
       <c r="F39" t="n">
-        <v>384.2650356824237</v>
+        <v>60.02261143999941</v>
       </c>
       <c r="G39" t="n">
-        <v>380.2250242210849</v>
+        <v>55.98259997866057</v>
       </c>
       <c r="H39" t="n">
         <v>51.92</v>
@@ -7277,13 +7277,13 @@
         <v>1846.683151095642</v>
       </c>
       <c r="U39" t="n">
-        <v>1766.721857646244</v>
+        <v>1591.376589078594</v>
       </c>
       <c r="V39" t="n">
-        <v>1672.26663826087</v>
+        <v>1496.92136969322</v>
       </c>
       <c r="W39" t="n">
-        <v>1559.768514109528</v>
+        <v>1384.423245541878</v>
       </c>
       <c r="X39" t="n">
         <v>1284.561892566739</v>
@@ -7378,22 +7378,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>597.1205880922942</v>
+        <v>596.6553483293503</v>
       </c>
       <c r="C41" t="n">
-        <v>467.3482868367447</v>
+        <v>466.8830470738009</v>
       </c>
       <c r="D41" t="n">
-        <v>377.106715382351</v>
+        <v>376.6414756194072</v>
       </c>
       <c r="E41" t="n">
-        <v>292.9013723451099</v>
+        <v>292.4361325821661</v>
       </c>
       <c r="F41" t="n">
-        <v>208.1643736501484</v>
+        <v>207.6991338872046</v>
       </c>
       <c r="G41" t="n">
-        <v>125.9679517166617</v>
+        <v>125.5027119537179</v>
       </c>
       <c r="H41" t="n">
         <v>51.92</v>
@@ -7405,49 +7405,49 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K41" t="n">
-        <v>307.5796384907274</v>
+        <v>775.9368380887173</v>
       </c>
       <c r="L41" t="n">
-        <v>523.631587033441</v>
+        <v>1009.32297330616</v>
       </c>
       <c r="M41" t="n">
-        <v>1114.38799366138</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="N41" t="n">
-        <v>1756.89799366138</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="O41" t="n">
-        <v>2399.40799366138</v>
+        <v>1812.963074689115</v>
       </c>
       <c r="P41" t="n">
-        <v>2596</v>
+        <v>2009.555081027735</v>
       </c>
       <c r="Q41" t="n">
         <v>2596</v>
       </c>
       <c r="R41" t="n">
-        <v>2596</v>
+        <v>2595.534760237057</v>
       </c>
       <c r="S41" t="n">
-        <v>2452.227270734164</v>
+        <v>2451.762030971221</v>
       </c>
       <c r="T41" t="n">
-        <v>2189.982954384821</v>
+        <v>2189.517714621877</v>
       </c>
       <c r="U41" t="n">
-        <v>1858.558041876961</v>
+        <v>1858.092802114017</v>
       </c>
       <c r="V41" t="n">
-        <v>1546.587310395321</v>
+        <v>1546.122070632377</v>
       </c>
       <c r="W41" t="n">
-        <v>1226.008041727697</v>
+        <v>1225.542801964753</v>
       </c>
       <c r="X41" t="n">
-        <v>951.9859877270223</v>
+        <v>951.5207479640785</v>
       </c>
       <c r="Y41" t="n">
-        <v>759.7461567342887</v>
+        <v>759.2809169713448</v>
       </c>
     </row>
     <row r="42">
@@ -7457,22 +7457,22 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>816.937701241021</v>
+        <v>168.4528527561725</v>
       </c>
       <c r="C42" t="n">
-        <v>776.43273917484</v>
+        <v>127.9478906899915</v>
       </c>
       <c r="D42" t="n">
-        <v>424.9805301872615</v>
+        <v>100.7381059448373</v>
       </c>
       <c r="E42" t="n">
         <v>78.84709864997603</v>
       </c>
       <c r="F42" t="n">
-        <v>60.0226114399994</v>
+        <v>60.02261143999941</v>
       </c>
       <c r="G42" t="n">
-        <v>55.98259997866058</v>
+        <v>55.98259997866057</v>
       </c>
       <c r="H42" t="n">
         <v>51.92</v>
@@ -7511,22 +7511,22 @@
         <v>1928.880474452383</v>
       </c>
       <c r="T42" t="n">
-        <v>1846.683151095641</v>
+        <v>1846.683151095642</v>
       </c>
       <c r="U42" t="n">
         <v>1766.721857646244</v>
       </c>
       <c r="V42" t="n">
-        <v>1496.92136969322</v>
+        <v>1348.024214018445</v>
       </c>
       <c r="W42" t="n">
-        <v>1384.423245541878</v>
+        <v>911.2836656246793</v>
       </c>
       <c r="X42" t="n">
-        <v>1284.561892566739</v>
+        <v>487.1798884071161</v>
       </c>
       <c r="Y42" t="n">
-        <v>1205.378667550442</v>
+        <v>407.9966633908188</v>
       </c>
     </row>
     <row r="43">
@@ -7572,19 +7572,19 @@
         <v>1505.227982468588</v>
       </c>
       <c r="N43" t="n">
-        <v>1349.248439584877</v>
+        <v>1348.401726605486</v>
       </c>
       <c r="O43" t="n">
-        <v>1115.142339091088</v>
+        <v>1114.295626111697</v>
       </c>
       <c r="P43" t="n">
-        <v>820.7766206439126</v>
+        <v>819.9299076645212</v>
       </c>
       <c r="Q43" t="n">
-        <v>464.3167555675508</v>
+        <v>463.4700425881596</v>
       </c>
       <c r="R43" t="n">
-        <v>82.79157247680381</v>
+        <v>81.94485949741255</v>
       </c>
       <c r="S43" t="n">
         <v>51.92</v>
@@ -7615,76 +7615,76 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922942</v>
       </c>
       <c r="C44" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367447</v>
       </c>
       <c r="D44" t="n">
-        <v>376.6414756194072</v>
+        <v>377.106715382351</v>
       </c>
       <c r="E44" t="n">
-        <v>292.4361325821661</v>
+        <v>292.9013723451099</v>
       </c>
       <c r="F44" t="n">
-        <v>207.6991338872046</v>
+        <v>208.1643736501484</v>
       </c>
       <c r="G44" t="n">
-        <v>125.5027119537179</v>
+        <v>125.9679517166617</v>
       </c>
       <c r="H44" t="n">
-        <v>51.92</v>
+        <v>52.3852397629438</v>
       </c>
       <c r="I44" t="n">
         <v>51.92</v>
       </c>
       <c r="J44" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K44" t="n">
-        <v>775.9368380887173</v>
+        <v>733.5813277110226</v>
       </c>
       <c r="L44" t="n">
-        <v>1418.446838088717</v>
+        <v>1009.32297330616</v>
       </c>
       <c r="M44" t="n">
-        <v>1418.446838088717</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="N44" t="n">
-        <v>1756.89799366138</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="O44" t="n">
-        <v>2399.40799366138</v>
+        <v>1812.963074689115</v>
       </c>
       <c r="P44" t="n">
-        <v>2596</v>
+        <v>2009.555081027735</v>
       </c>
       <c r="Q44" t="n">
         <v>2596</v>
       </c>
       <c r="R44" t="n">
-        <v>2595.534760237057</v>
+        <v>2596</v>
       </c>
       <c r="S44" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T44" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U44" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V44" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.587310395321</v>
       </c>
       <c r="W44" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X44" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270223</v>
       </c>
       <c r="Y44" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342887</v>
       </c>
     </row>
     <row r="45">
@@ -7694,22 +7694,22 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1316.525394051095</v>
+        <v>492.6952769985968</v>
       </c>
       <c r="C45" t="n">
-        <v>1100.675163417264</v>
+        <v>127.9478906899915</v>
       </c>
       <c r="D45" t="n">
-        <v>749.2229544296858</v>
+        <v>100.7381059448373</v>
       </c>
       <c r="E45" t="n">
-        <v>403.0895228924003</v>
+        <v>78.84709864997603</v>
       </c>
       <c r="F45" t="n">
-        <v>60.02261143999941</v>
+        <v>60.0226114399994</v>
       </c>
       <c r="G45" t="n">
-        <v>55.98259997866057</v>
+        <v>55.98259997866058</v>
       </c>
       <c r="H45" t="n">
         <v>51.92</v>
@@ -7748,7 +7748,7 @@
         <v>1928.880474452383</v>
       </c>
       <c r="T45" t="n">
-        <v>1846.683151095642</v>
+        <v>1846.683151095641</v>
       </c>
       <c r="U45" t="n">
         <v>1766.721857646244</v>
@@ -7760,10 +7760,10 @@
         <v>1559.768514109528</v>
       </c>
       <c r="X45" t="n">
-        <v>1459.907161134389</v>
+        <v>1284.561892566739</v>
       </c>
       <c r="Y45" t="n">
-        <v>1380.723936118092</v>
+        <v>881.1362433080176</v>
       </c>
     </row>
     <row r="46">
@@ -7815,13 +7815,13 @@
         <v>1114.295626111697</v>
       </c>
       <c r="P46" t="n">
-        <v>819.9299076645212</v>
+        <v>819.9299076645211</v>
       </c>
       <c r="Q46" t="n">
-        <v>463.4700425881596</v>
+        <v>463.4700425881595</v>
       </c>
       <c r="R46" t="n">
-        <v>81.94485949741255</v>
+        <v>81.94485949741244</v>
       </c>
       <c r="S46" t="n">
         <v>51.92</v>
@@ -7964,28 +7964,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>359.1293926214164</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>321.8400703517588</v>
+        <v>320.3286984924623</v>
       </c>
       <c r="L2" t="n">
-        <v>309.2909949748744</v>
+        <v>233.2284144914465</v>
       </c>
       <c r="M2" t="n">
-        <v>472.2608914614128</v>
+        <v>844.554996989051</v>
       </c>
       <c r="N2" t="n">
-        <v>404.0826666125488</v>
+        <v>403.3653500296342</v>
       </c>
       <c r="O2" t="n">
-        <v>1.159015302735668</v>
+        <v>373.4816735941929</v>
       </c>
       <c r="P2" t="n">
-        <v>315.3213213472141</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>128.5418702571336</v>
+        <v>128.1077446289929</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8043,7 +8043,7 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J3" t="n">
-        <v>227.4647419277884</v>
+        <v>223.7070799393696</v>
       </c>
       <c r="K3" t="n">
         <v>295.8802408630135</v>
@@ -8201,28 +8201,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2405037325275146</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>321.8400703517588</v>
+        <v>321.3286984924623</v>
       </c>
       <c r="L5" t="n">
-        <v>309.2909949748743</v>
+        <v>308.6565929648241</v>
       </c>
       <c r="M5" t="n">
-        <v>846.2608914614127</v>
+        <v>771.0864144752693</v>
       </c>
       <c r="N5" t="n">
-        <v>704.292876848652</v>
+        <v>403.3653500296342</v>
       </c>
       <c r="O5" t="n">
-        <v>1.159015302735668</v>
+        <v>0.4816735941929551</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>128.5418702571336</v>
+        <v>502.1077446289929</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8441,7 +8441,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>306.1168901088537</v>
+        <v>321.3286984924623</v>
       </c>
       <c r="L8" t="n">
         <v>308.6565929648241</v>
@@ -8450,13 +8450,13 @@
         <v>845.554996989051</v>
       </c>
       <c r="N8" t="n">
-        <v>403.3653500296342</v>
+        <v>702.8967675158527</v>
       </c>
       <c r="O8" t="n">
         <v>0.4816735941929551</v>
       </c>
       <c r="P8" t="n">
-        <v>314.7432258698271</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>128.1077446289929</v>
@@ -8675,25 +8675,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>473.08808040201</v>
+        <v>473.0880804020101</v>
       </c>
       <c r="L11" t="n">
         <v>430.7657085427136</v>
       </c>
       <c r="M11" t="n">
-        <v>301.434429149855</v>
+        <v>480.5466050990546</v>
       </c>
       <c r="N11" t="n">
-        <v>230.4920535472222</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>397.8074393630432</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>23.48346824708341</v>
@@ -8915,7 +8915,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K14" t="n">
-        <v>473.08808040201</v>
+        <v>278.5269147425628</v>
       </c>
       <c r="L14" t="n">
         <v>430.7657085427136</v>
@@ -8933,7 +8933,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>421.2909076101267</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9149,28 +9149,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>473.08808040201</v>
+        <v>473.0880804020101</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>430.7657085427136</v>
       </c>
       <c r="M17" t="n">
-        <v>301.434429149855</v>
+        <v>480.5466050990546</v>
       </c>
       <c r="N17" t="n">
-        <v>230.4920535472222</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>236.2045428832664</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>615.8520732695737</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9386,19 +9386,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K20" t="n">
-        <v>3.200256351209731</v>
+        <v>473.08808040201</v>
       </c>
       <c r="L20" t="n">
-        <v>430.7657085427136</v>
+        <v>236.2045428832664</v>
       </c>
       <c r="M20" t="n">
-        <v>950.4344291498551</v>
+        <v>301.434429149855</v>
       </c>
       <c r="N20" t="n">
-        <v>879.4920535472222</v>
+        <v>230.4920535472222</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -9407,7 +9407,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>23.48346824708341</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9632,13 +9632,13 @@
         <v>430.7657085427136</v>
       </c>
       <c r="M23" t="n">
-        <v>301.434429149855</v>
+        <v>480.5466050990546</v>
       </c>
       <c r="N23" t="n">
         <v>879.4920535472222</v>
       </c>
       <c r="O23" t="n">
-        <v>179.1121759491996</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
@@ -9863,19 +9863,19 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>473.0880804020101</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>430.7657085427136</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>950.4344291498551</v>
+        <v>898.1580722083796</v>
       </c>
       <c r="N26" t="n">
-        <v>409.6042294964216</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>486.2423218353989</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -10100,25 +10100,25 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>473.0880804020101</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>430.7657085427136</v>
       </c>
       <c r="M29" t="n">
-        <v>504.3672513663132</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N29" t="n">
-        <v>230.4920535472222</v>
+        <v>409.6042294964216</v>
       </c>
       <c r="O29" t="n">
-        <v>486.2423218353989</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>450.422215819576</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>615.8520732695737</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10343,10 +10343,10 @@
         <v>430.7657085427136</v>
       </c>
       <c r="M32" t="n">
-        <v>301.434429149855</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N32" t="n">
-        <v>466.2356244739315</v>
+        <v>409.6042294964216</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -10355,7 +10355,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>615.8520732695737</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10574,13 +10574,13 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>473.0880804020101</v>
+        <v>59.83165132871943</v>
       </c>
       <c r="L35" t="n">
         <v>430.7657085427136</v>
       </c>
       <c r="M35" t="n">
-        <v>301.434429149855</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N35" t="n">
         <v>230.4920535472222</v>
@@ -10589,7 +10589,7 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>235.7435709267094</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>615.8520732695737</v>
@@ -10808,16 +10808,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>473.0880804020101</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>430.7657085427136</v>
       </c>
       <c r="M38" t="n">
-        <v>560.3048366155554</v>
+        <v>537.1780000765643</v>
       </c>
       <c r="N38" t="n">
         <v>230.4920535472222</v>
@@ -10826,7 +10826,7 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>450.422215819576</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
         <v>615.8520732695737</v>
@@ -11048,25 +11048,25 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>473.0880804020101</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>17.50927946942295</v>
       </c>
       <c r="M41" t="n">
-        <v>898.1580722083796</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N41" t="n">
-        <v>879.4920535472222</v>
+        <v>230.4920535472222</v>
       </c>
       <c r="O41" t="n">
-        <v>486.2423218353989</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>23.48346824708341</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11282,28 +11282,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K44" t="n">
-        <v>473.0880804020101</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>430.7657085427136</v>
+        <v>60.29262328527625</v>
       </c>
       <c r="M44" t="n">
-        <v>301.434429149855</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N44" t="n">
-        <v>572.361907661023</v>
+        <v>230.4920535472222</v>
       </c>
       <c r="O44" t="n">
-        <v>486.2423218353989</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>23.48346824708341</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -22512,7 +22512,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>1.927393539208538</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -23411,10 +23411,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0.8382458495976817</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>0.8382458495977119</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -23669,7 +23669,7 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8382458495973424</v>
+        <v>0.8382458495974596</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -24122,7 +24122,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>0.8382458495976959</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -24143,7 +24143,7 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.8382458495974596</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -24380,7 +24380,7 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0.8382458495973424</v>
+        <v>0.8382458495974596</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -24596,7 +24596,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0.8382458495976959</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -24617,7 +24617,7 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>0.8382458495973424</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -24833,7 +24833,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0.8382458495976817</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -24854,7 +24854,7 @@
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>0.8382458495973424</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -25787,7 +25787,7 @@
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>0.8382458495976266</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -25802,7 +25802,7 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>0.8382458495973424</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -26039,7 +26039,7 @@
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>0.8382458495973424</v>
+        <v>0.8382458495974596</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -26086,7 +26086,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>797725.6530297217</v>
+        <v>797448.2902684262</v>
       </c>
     </row>
     <row r="3">
@@ -26094,7 +26094,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1521867.451220963</v>
+        <v>1521696.852918674</v>
       </c>
     </row>
     <row r="4">
@@ -26102,7 +26102,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2245926.867912206</v>
+        <v>2245838.651109917</v>
       </c>
     </row>
     <row r="5">
@@ -26110,7 +26110,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2969705.156810724</v>
+        <v>2969616.940008434</v>
       </c>
     </row>
     <row r="6">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>3693835.387209242</v>
+        <v>3693747.170406953</v>
       </c>
     </row>
     <row r="7">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4417965.617607759</v>
+        <v>4417877.40080547</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5142095.848006274</v>
+        <v>5142007.631203984</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5866226.078404788</v>
+        <v>5866137.861602499</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6590356.308803302</v>
+        <v>6590268.092001013</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7314486.539201817</v>
+        <v>7314398.322399528</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>8038616.769600337</v>
+        <v>8038528.552798048</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8762746.999998862</v>
+        <v>8762658.783196572</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>9486877.230397385</v>
+        <v>9486789.013595095</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>10211007.46079591</v>
+        <v>10210919.24399362</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>10935137.69119443</v>
+        <v>10935049.47439214</v>
       </c>
     </row>
   </sheetData>
@@ -26269,7 +26269,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1479768.022390799</v>
+        <v>1479587.753273077</v>
       </c>
       <c r="C2" t="n">
         <v>1479768.022390799</v>
@@ -26290,7 +26290,7 @@
         <v>1479744.38385784</v>
       </c>
       <c r="I2" t="n">
-        <v>1479744.383857841</v>
+        <v>1479744.38385784</v>
       </c>
       <c r="J2" t="n">
         <v>1479744.38385784</v>
@@ -26308,7 +26308,7 @@
         <v>1479744.383857841</v>
       </c>
       <c r="O2" t="n">
-        <v>1479744.383857839</v>
+        <v>1479744.383857841</v>
       </c>
       <c r="P2" t="n">
         <v>1479744.38385784</v>
@@ -26321,13 +26321,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>231098</v>
+        <v>231721</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>352</v>
       </c>
       <c r="D3" t="n">
-        <v>975</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>588575</v>
@@ -26345,10 +26345,10 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>388448</v>
+        <v>388096</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>352</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>577464.9346667652</v>
+        <v>570823.1065049333</v>
       </c>
       <c r="C4" t="n">
-        <v>575456.0124792766</v>
+        <v>568738.1032495913</v>
       </c>
       <c r="D4" t="n">
-        <v>573221.1009892205</v>
+        <v>566727.0147207876</v>
       </c>
       <c r="E4" t="n">
-        <v>489938.9797961749</v>
+        <v>483475.9886658207</v>
       </c>
       <c r="F4" t="n">
-        <v>488252.9169779522</v>
+        <v>481789.9258475979</v>
       </c>
       <c r="G4" t="n">
-        <v>486564.5274562991</v>
+        <v>480101.5363259449</v>
       </c>
       <c r="H4" t="n">
-        <v>484873.7945463364</v>
+        <v>478410.8034159822</v>
       </c>
       <c r="I4" t="n">
-        <v>483180.7013457892</v>
+        <v>476717.710215435</v>
       </c>
       <c r="J4" t="n">
-        <v>481485.2307308645</v>
+        <v>475022.2396005102</v>
       </c>
       <c r="K4" t="n">
-        <v>479787.365352031</v>
+        <v>473324.3742216767</v>
       </c>
       <c r="L4" t="n">
-        <v>478087.087629687</v>
+        <v>471624.0964993328</v>
       </c>
       <c r="M4" t="n">
-        <v>476384.3797497193</v>
+        <v>469921.3886193651</v>
       </c>
       <c r="N4" t="n">
-        <v>474679.2236589555</v>
+        <v>468216.2325286012</v>
       </c>
       <c r="O4" t="n">
-        <v>472971.6010604933</v>
+        <v>466508.6099301392</v>
       </c>
       <c r="P4" t="n">
-        <v>471261.4934089099</v>
+        <v>464798.5022785557</v>
       </c>
     </row>
     <row r="5">
@@ -26425,10 +26425,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>58590.39999999999</v>
+        <v>58551.39999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>58590.39999999999</v>
+        <v>58612.2</v>
       </c>
       <c r="D5" t="n">
         <v>58612.2</v>
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>612614.687724034</v>
+        <v>618492.2467681437</v>
       </c>
       <c r="C6" t="n">
-        <v>845721.6099115227</v>
+        <v>852065.7191412074</v>
       </c>
       <c r="D6" t="n">
-        <v>846959.7214015789</v>
+        <v>854428.8076700113</v>
       </c>
       <c r="E6" t="n">
-        <v>327285.8550616648</v>
+        <v>333748.8461920198</v>
       </c>
       <c r="F6" t="n">
-        <v>917546.9178798882</v>
+        <v>924009.9090102423</v>
       </c>
       <c r="G6" t="n">
-        <v>919235.3074015409</v>
+        <v>925698.2985318952</v>
       </c>
       <c r="H6" t="n">
-        <v>920926.0403115033</v>
+        <v>927389.0314418583</v>
       </c>
       <c r="I6" t="n">
-        <v>922619.1335120514</v>
+        <v>929082.124642405</v>
       </c>
       <c r="J6" t="n">
-        <v>535866.604126976</v>
+        <v>542681.5952573302</v>
       </c>
       <c r="K6" t="n">
-        <v>926012.4695058092</v>
+        <v>932123.4606361637</v>
       </c>
       <c r="L6" t="n">
-        <v>927712.7472281525</v>
+        <v>934175.738358507</v>
       </c>
       <c r="M6" t="n">
-        <v>832615.4551081205</v>
+        <v>839078.4462384749</v>
       </c>
       <c r="N6" t="n">
-        <v>931120.6111988855</v>
+        <v>937583.6023292396</v>
       </c>
       <c r="O6" t="n">
-        <v>676028.2337973459</v>
+        <v>682491.2249277015</v>
       </c>
       <c r="P6" t="n">
-        <v>934538.3414489303</v>
+        <v>941001.3325792839</v>
       </c>
     </row>
   </sheetData>
@@ -26807,10 +26807,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D3" t="n">
         <v>103</v>
@@ -26859,7 +26859,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C4" t="n">
         <v>374</v>
@@ -26984,7 +26984,7 @@
         <v>321</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>-0</v>
@@ -26993,7 +26993,7 @@
         <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J2" t="n">
         <v>321</v>
@@ -27002,7 +27002,7 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>-0</v>
@@ -27024,13 +27024,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C3" t="n">
         <v>-0</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>-0</v>
       </c>
       <c r="E3" t="n">
         <v>241</v>
@@ -27076,10 +27076,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
         <v>-0</v>
@@ -27100,13 +27100,13 @@
         <v>-0</v>
       </c>
       <c r="J4" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
         <v>-0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>275</v>
@@ -27317,10 +27317,10 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -27454,7 +27454,7 @@
         <v>400</v>
       </c>
       <c r="I2" t="n">
-        <v>132.4740095033003</v>
+        <v>134.1177124465037</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27481,7 +27481,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>225.120779732817</v>
+        <v>224.8682520946261</v>
       </c>
       <c r="S2" t="n">
         <v>400</v>
@@ -27524,16 +27524,16 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
-        <v>325.5201396486123</v>
+        <v>325.517988705216</v>
       </c>
       <c r="H3" t="n">
-        <v>330.0491815260438</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>209.5726123064429</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27560,13 +27560,13 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>400</v>
+        <v>246.8340298130979</v>
       </c>
       <c r="S3" t="n">
         <v>400</v>
       </c>
       <c r="T3" t="n">
-        <v>388.3280728909799</v>
+        <v>400</v>
       </c>
       <c r="U3" t="n">
         <v>400</v>
@@ -27575,7 +27575,7 @@
         <v>400</v>
       </c>
       <c r="W3" t="n">
-        <v>58.37314290982852</v>
+        <v>400</v>
       </c>
       <c r="X3" t="n">
         <v>400</v>
@@ -27591,37 +27591,37 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>287.1138003370787</v>
+      </c>
+      <c r="C4" t="n">
+        <v>341.3946299245686</v>
+      </c>
+      <c r="D4" t="n">
         <v>400</v>
       </c>
-      <c r="C4" t="n">
-        <v>272.7252466480447</v>
-      </c>
-      <c r="D4" t="n">
-        <v>285.5362180555555</v>
-      </c>
       <c r="E4" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F4" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G4" t="n">
-        <v>244.8599384153005</v>
+        <v>400</v>
       </c>
       <c r="H4" t="n">
         <v>400</v>
       </c>
       <c r="I4" t="n">
-        <v>400</v>
+        <v>171.047816275856</v>
       </c>
       <c r="J4" t="n">
-        <v>396.2647849014816</v>
+        <v>22.13729309820286</v>
       </c>
       <c r="K4" t="n">
-        <v>400</v>
+        <v>266.941429538848</v>
       </c>
       <c r="L4" t="n">
-        <v>400</v>
+        <v>395.9334970102382</v>
       </c>
       <c r="M4" t="n">
         <v>400</v>
@@ -27642,22 +27642,22 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
-        <v>400</v>
+        <v>359.1365780635112</v>
       </c>
       <c r="T4" t="n">
         <v>400</v>
       </c>
       <c r="U4" t="n">
-        <v>150.9483584875727</v>
+        <v>400</v>
       </c>
       <c r="V4" t="n">
         <v>199.1703102162162</v>
       </c>
       <c r="W4" t="n">
-        <v>226.3728098387097</v>
+        <v>400</v>
       </c>
       <c r="X4" t="n">
-        <v>361.0833124900162</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y4" t="n">
         <v>287.4653528494624</v>
@@ -27691,7 +27691,7 @@
         <v>400</v>
       </c>
       <c r="I5" t="n">
-        <v>132.4740095033003</v>
+        <v>134.1177124465037</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27718,10 +27718,10 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>225.120779732817</v>
+        <v>224.8682520946261</v>
       </c>
       <c r="S5" t="n">
-        <v>400</v>
+        <v>398.0465935392085</v>
       </c>
       <c r="T5" t="n">
         <v>400</v>
@@ -27755,7 +27755,7 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
-        <v>207.7841109576156</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
         <v>342.6720972219126</v>
@@ -27764,13 +27764,13 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
-        <v>325.5201396486123</v>
+        <v>325.517988705216</v>
       </c>
       <c r="H6" t="n">
-        <v>330.0491815260438</v>
+        <v>330.0284079411381</v>
       </c>
       <c r="I6" t="n">
-        <v>209.5726123064429</v>
+        <v>209.4985557026693</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -27794,16 +27794,16 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>145.073529241423</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>400</v>
       </c>
       <c r="S6" t="n">
-        <v>88.48881128536601</v>
+        <v>400</v>
       </c>
       <c r="T6" t="n">
-        <v>30.47344446279683</v>
+        <v>400</v>
       </c>
       <c r="U6" t="n">
         <v>400</v>
@@ -27815,10 +27815,10 @@
         <v>400</v>
       </c>
       <c r="X6" t="n">
-        <v>400</v>
+        <v>45.86273944538755</v>
       </c>
       <c r="Y6" t="n">
-        <v>399.3913927661343</v>
+        <v>73.97007056175499</v>
       </c>
     </row>
     <row r="7">
@@ -27828,19 +27828,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C7" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D7" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E7" t="n">
         <v>400</v>
       </c>
       <c r="F7" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G7" t="n">
         <v>400</v>
@@ -27852,13 +27852,13 @@
         <v>400</v>
       </c>
       <c r="J7" t="n">
-        <v>396.2647849014816</v>
+        <v>102.0829392600466</v>
       </c>
       <c r="K7" t="n">
         <v>400</v>
       </c>
       <c r="L7" t="n">
-        <v>400</v>
+        <v>395.9334970102382</v>
       </c>
       <c r="M7" t="n">
         <v>400</v>
@@ -27879,13 +27879,13 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>359.1680042930194</v>
+        <v>359.1365780635112</v>
       </c>
       <c r="T7" t="n">
-        <v>209.2386648669134</v>
+        <v>209.2309599488807</v>
       </c>
       <c r="U7" t="n">
-        <v>182.3520447328345</v>
+        <v>150.9482601269169</v>
       </c>
       <c r="V7" t="n">
         <v>199.1703102162162</v>
@@ -27894,7 +27894,7 @@
         <v>226.3728098387097</v>
       </c>
       <c r="X7" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y7" t="n">
         <v>287.4653528494624</v>
@@ -27925,10 +27925,10 @@
         <v>400</v>
       </c>
       <c r="H8" t="n">
-        <v>400</v>
+        <v>398.0465935392086</v>
       </c>
       <c r="I8" t="n">
-        <v>132.1643059857123</v>
+        <v>134.1177124465037</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27989,22 +27989,22 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C9" t="n">
-        <v>133.1656676742304</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>325.517988705216</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>330.0284079411381</v>
+        <v>298.8068206386721</v>
       </c>
       <c r="I9" t="n">
         <v>209.4985557026693</v>
@@ -28031,10 +28031,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>144.7989632036872</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>159.5184388018133</v>
+        <v>400</v>
       </c>
       <c r="S9" t="n">
         <v>400</v>
@@ -28043,13 +28043,13 @@
         <v>400</v>
       </c>
       <c r="U9" t="n">
-        <v>26.19578428848864</v>
+        <v>400</v>
       </c>
       <c r="V9" t="n">
         <v>400</v>
       </c>
       <c r="W9" t="n">
-        <v>58.37314290982852</v>
+        <v>400</v>
       </c>
       <c r="X9" t="n">
         <v>400</v>
@@ -28071,25 +28071,25 @@
         <v>272.7252466480447</v>
       </c>
       <c r="D10" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E10" t="n">
         <v>280.9809048369565</v>
       </c>
       <c r="F10" t="n">
-        <v>400</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G10" t="n">
-        <v>400</v>
+        <v>244.858135136612</v>
       </c>
       <c r="H10" t="n">
-        <v>400</v>
+        <v>227.1197490524383</v>
       </c>
       <c r="I10" t="n">
         <v>171.047816275856</v>
       </c>
       <c r="J10" t="n">
-        <v>396.1372930982029</v>
+        <v>387.1201128983657</v>
       </c>
       <c r="K10" t="n">
         <v>266.941429538848</v>
@@ -28116,19 +28116,19 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
-        <v>359.1365780635112</v>
+        <v>400</v>
       </c>
       <c r="T10" t="n">
+        <v>209.2309599488807</v>
+      </c>
+      <c r="U10" t="n">
         <v>400</v>
       </c>
-      <c r="U10" t="n">
-        <v>150.9482601269169</v>
-      </c>
       <c r="V10" t="n">
-        <v>324.5806538211425</v>
+        <v>400</v>
       </c>
       <c r="W10" t="n">
-        <v>226.3728098387097</v>
+        <v>400</v>
       </c>
       <c r="X10" t="n">
         <v>247.4436454301076</v>
@@ -28162,7 +28162,7 @@
         <v>321</v>
       </c>
       <c r="H11" t="n">
-        <v>320.5394126346856</v>
+        <v>320.5394126346858</v>
       </c>
       <c r="I11" t="n">
         <v>96.76634561233286</v>
@@ -28226,19 +28226,19 @@
         <v>321</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D12" t="n">
         <v>321</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F12" t="n">
         <v>321</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>226.0367322273742</v>
       </c>
       <c r="H12" t="n">
         <v>321</v>
@@ -28268,13 +28268,13 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
         <v>321</v>
@@ -28283,13 +28283,13 @@
         <v>321</v>
       </c>
       <c r="V12" t="n">
-        <v>147.4081841180271</v>
+        <v>321</v>
       </c>
       <c r="W12" t="n">
         <v>321</v>
       </c>
       <c r="X12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>321</v>
@@ -28399,7 +28399,7 @@
         <v>321</v>
       </c>
       <c r="H14" t="n">
-        <v>320.5394126346858</v>
+        <v>321</v>
       </c>
       <c r="I14" t="n">
         <v>96.76634561233286</v>
@@ -28429,7 +28429,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>164.009091290606</v>
+        <v>163.5485039252921</v>
       </c>
       <c r="S14" t="n">
         <v>321</v>
@@ -28460,7 +28460,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C15" t="n">
         <v>321</v>
@@ -28469,16 +28469,16 @@
         <v>321</v>
       </c>
       <c r="E15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
         <v>321</v>
       </c>
       <c r="G15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>321</v>
+        <v>147.408184118027</v>
       </c>
       <c r="I15" t="n">
         <v>191.6509141932353</v>
@@ -28517,13 +28517,13 @@
         <v>321</v>
       </c>
       <c r="U15" t="n">
-        <v>147.4081841180266</v>
+        <v>321</v>
       </c>
       <c r="V15" t="n">
         <v>321</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -28636,10 +28636,10 @@
         <v>321</v>
       </c>
       <c r="H17" t="n">
-        <v>320.5394126346856</v>
+        <v>321</v>
       </c>
       <c r="I17" t="n">
-        <v>96.76634561233286</v>
+        <v>96.3057582470185</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -28697,11 +28697,11 @@
         </is>
       </c>
       <c r="B18" t="n">
+        <v>321</v>
+      </c>
+      <c r="C18" t="n">
         <v>147.4081841180271</v>
       </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
@@ -28709,7 +28709,7 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
         <v>321</v>
@@ -28876,7 +28876,7 @@
         <v>321</v>
       </c>
       <c r="I20" t="n">
-        <v>96.3057582470185</v>
+        <v>96.3057582470187</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -28934,16 +28934,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>321</v>
+        <v>147.4081841180269</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
         <v>321</v>
@@ -28994,16 +28994,16 @@
         <v>321</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="W21" t="n">
         <v>321</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="Y21" t="n">
-        <v>147.4081841180265</v>
+        <v>321</v>
       </c>
     </row>
     <row r="22">
@@ -29110,7 +29110,7 @@
         <v>321</v>
       </c>
       <c r="H23" t="n">
-        <v>320.5394126346858</v>
+        <v>321</v>
       </c>
       <c r="I23" t="n">
         <v>96.76634561233286</v>
@@ -29140,7 +29140,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>164.009091290606</v>
+        <v>163.5485039252921</v>
       </c>
       <c r="S23" t="n">
         <v>321</v>
@@ -29171,19 +29171,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>147.4081841180271</v>
       </c>
       <c r="C24" t="n">
         <v>321</v>
       </c>
       <c r="D24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
         <v>321</v>
@@ -29228,13 +29228,13 @@
         <v>321</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="W24" t="n">
-        <v>147.4081841180268</v>
+        <v>321</v>
       </c>
       <c r="X24" t="n">
         <v>321</v>
@@ -29350,7 +29350,7 @@
         <v>321</v>
       </c>
       <c r="I26" t="n">
-        <v>96.3057582470187</v>
+        <v>96.76634561233286</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -29377,7 +29377,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>164.009091290606</v>
+        <v>163.5485039252921</v>
       </c>
       <c r="S26" t="n">
         <v>321</v>
@@ -29408,16 +29408,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>147.4081841180269</v>
       </c>
       <c r="C27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
         <v>321</v>
@@ -29429,7 +29429,7 @@
         <v>321</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>191.6509141932353</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -29465,10 +29465,10 @@
         <v>321</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="V27" t="n">
-        <v>18.05909831126235</v>
+        <v>321</v>
       </c>
       <c r="W27" t="n">
         <v>321</v>
@@ -29584,7 +29584,7 @@
         <v>321</v>
       </c>
       <c r="H29" t="n">
-        <v>321</v>
+        <v>320.5394126346858</v>
       </c>
       <c r="I29" t="n">
         <v>96.76634561233286</v>
@@ -29614,7 +29614,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>163.5485039252921</v>
+        <v>164.009091290606</v>
       </c>
       <c r="S29" t="n">
         <v>321</v>
@@ -29648,7 +29648,7 @@
         <v>321</v>
       </c>
       <c r="C30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
         <v>321</v>
@@ -29657,7 +29657,7 @@
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>147.4081841180267</v>
       </c>
       <c r="G30" t="n">
         <v>321</v>
@@ -29714,7 +29714,7 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>147.408184118027</v>
+        <v>321</v>
       </c>
     </row>
     <row r="31">
@@ -29821,7 +29821,7 @@
         <v>321</v>
       </c>
       <c r="H32" t="n">
-        <v>321</v>
+        <v>320.5394126346856</v>
       </c>
       <c r="I32" t="n">
         <v>96.76634561233286</v>
@@ -29851,7 +29851,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>163.5485039252921</v>
+        <v>164.009091290606</v>
       </c>
       <c r="S32" t="n">
         <v>321</v>
@@ -29882,19 +29882,19 @@
         </is>
       </c>
       <c r="B33" t="n">
+        <v>321</v>
+      </c>
+      <c r="C33" t="n">
         <v>147.4081841180271</v>
       </c>
-      <c r="C33" t="n">
-        <v>0</v>
-      </c>
       <c r="D33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
         <v>321</v>
@@ -29945,7 +29945,7 @@
         <v>321</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="X33" t="n">
         <v>321</v>
@@ -30122,13 +30122,13 @@
         <v>321</v>
       </c>
       <c r="C36" t="n">
-        <v>321</v>
+        <v>147.4081841180271</v>
       </c>
       <c r="D36" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -30164,22 +30164,22 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="S36" t="n">
         <v>321</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="U36" t="n">
         <v>321</v>
       </c>
       <c r="V36" t="n">
-        <v>226.0367322273742</v>
+        <v>321</v>
       </c>
       <c r="W36" t="n">
         <v>321</v>
@@ -30325,10 +30325,10 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>163.5485039252921</v>
+        <v>164.009091290606</v>
       </c>
       <c r="S38" t="n">
-        <v>321</v>
+        <v>320.539412634686</v>
       </c>
       <c r="T38" t="n">
         <v>321</v>
@@ -30368,13 +30368,13 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
         <v>321</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="I39" t="n">
         <v>191.6509141932353</v>
@@ -30413,7 +30413,7 @@
         <v>321</v>
       </c>
       <c r="U39" t="n">
-        <v>321</v>
+        <v>147.4081841180269</v>
       </c>
       <c r="V39" t="n">
         <v>321</v>
@@ -30422,7 +30422,7 @@
         <v>321</v>
       </c>
       <c r="X39" t="n">
-        <v>147.4081841180269</v>
+        <v>321</v>
       </c>
       <c r="Y39" t="n">
         <v>321</v>
@@ -30532,7 +30532,7 @@
         <v>321</v>
       </c>
       <c r="H41" t="n">
-        <v>320.5394126346856</v>
+        <v>321</v>
       </c>
       <c r="I41" t="n">
         <v>96.76634561233286</v>
@@ -30562,7 +30562,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>164.009091290606</v>
+        <v>163.5485039252921</v>
       </c>
       <c r="S41" t="n">
         <v>321</v>
@@ -30593,16 +30593,16 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>147.4081841180269</v>
       </c>
       <c r="C42" t="n">
         <v>321</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F42" t="n">
         <v>321</v>
@@ -30653,13 +30653,13 @@
         <v>321</v>
       </c>
       <c r="V42" t="n">
-        <v>147.4081841180268</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
         <v>321</v>
@@ -30772,7 +30772,7 @@
         <v>321</v>
       </c>
       <c r="I44" t="n">
-        <v>96.76634561233286</v>
+        <v>96.3057582470185</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -30799,7 +30799,7 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>163.5485039252921</v>
+        <v>164.009091290606</v>
       </c>
       <c r="S44" t="n">
         <v>321</v>
@@ -30830,19 +30830,19 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>147.4081841180269</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G45" t="n">
         <v>321</v>
@@ -30896,10 +30896,10 @@
         <v>321</v>
       </c>
       <c r="X45" t="n">
-        <v>321</v>
+        <v>147.4081841180269</v>
       </c>
       <c r="Y45" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -31091,49 +31091,49 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4100502512562811</v>
+        <v>0.4140703517587936</v>
       </c>
       <c r="H2" t="n">
-        <v>4.199427135678389</v>
+        <v>4.240597989949746</v>
       </c>
       <c r="I2" t="n">
-        <v>15.80846231155779</v>
+        <v>15.96344723618091</v>
       </c>
       <c r="J2" t="n">
-        <v>34.80250251256282</v>
+        <v>35.14370351758794</v>
       </c>
       <c r="K2" t="n">
-        <v>52.15992964824121</v>
+        <v>52.67130150753769</v>
       </c>
       <c r="L2" t="n">
-        <v>64.70900502512563</v>
+        <v>65.34340703517589</v>
       </c>
       <c r="M2" t="n">
-        <v>72.00123618090453</v>
+        <v>72.70713065326633</v>
       </c>
       <c r="N2" t="n">
-        <v>73.16629145728643</v>
+        <v>73.88360804020101</v>
       </c>
       <c r="O2" t="n">
-        <v>69.08885427135678</v>
+        <v>69.76619597989949</v>
       </c>
       <c r="P2" t="n">
-        <v>58.96573869346734</v>
+        <v>59.54383417085427</v>
       </c>
       <c r="Q2" t="n">
-        <v>44.28081407035176</v>
+        <v>44.71493969849246</v>
       </c>
       <c r="R2" t="n">
-        <v>25.75781909547739</v>
+        <v>26.01034673366835</v>
       </c>
       <c r="S2" t="n">
-        <v>9.344020100502515</v>
+        <v>9.435628140703519</v>
       </c>
       <c r="T2" t="n">
-        <v>1.794994974874371</v>
+        <v>1.81259296482412</v>
       </c>
       <c r="U2" t="n">
-        <v>0.03280402010050248</v>
+        <v>0.03312562814070349</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -31170,49 +31170,49 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2193962264150943</v>
+        <v>0.2215471698113208</v>
       </c>
       <c r="H3" t="n">
-        <v>2.118905660377359</v>
+        <v>2.139679245283019</v>
       </c>
       <c r="I3" t="n">
-        <v>7.553773584905661</v>
+        <v>7.627830188679247</v>
       </c>
       <c r="J3" t="n">
-        <v>20.7281320754717</v>
+        <v>20.93134905660378</v>
       </c>
       <c r="K3" t="n">
-        <v>35.42767924528302</v>
+        <v>35.77500943396227</v>
       </c>
       <c r="L3" t="n">
-        <v>47.63688679245283</v>
+        <v>48.10391509433963</v>
       </c>
       <c r="M3" t="n">
-        <v>55.58999999999999</v>
+        <v>56.13499999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>57.06130188679246</v>
+        <v>57.62072641509435</v>
       </c>
       <c r="O3" t="n">
-        <v>52.19994339622642</v>
+        <v>52.71170754716981</v>
       </c>
       <c r="P3" t="n">
-        <v>41.89505660377359</v>
+        <v>42.3057924528302</v>
       </c>
       <c r="Q3" t="n">
-        <v>28.00573584905661</v>
+        <v>28.28030188679246</v>
       </c>
       <c r="R3" t="n">
-        <v>13.62181132075472</v>
+        <v>13.75535849056604</v>
       </c>
       <c r="S3" t="n">
-        <v>4.07518867924528</v>
+        <v>4.115141509433959</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8843207547169808</v>
+        <v>0.8929905660377355</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01443396226415095</v>
+        <v>0.01457547169811321</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -31249,49 +31249,49 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1839344262295082</v>
+        <v>0.1857377049180328</v>
       </c>
       <c r="H4" t="n">
-        <v>1.635344262295083</v>
+        <v>1.651377049180329</v>
       </c>
       <c r="I4" t="n">
-        <v>5.531409836065575</v>
+        <v>5.585639344262296</v>
       </c>
       <c r="J4" t="n">
-        <v>13.00416393442623</v>
+        <v>13.13165573770492</v>
       </c>
       <c r="K4" t="n">
-        <v>21.36983606557376</v>
+        <v>21.57934426229507</v>
       </c>
       <c r="L4" t="n">
-        <v>27.34603278688525</v>
+        <v>27.61413114754098</v>
       </c>
       <c r="M4" t="n">
-        <v>28.83255737704917</v>
+        <v>29.11522950819672</v>
       </c>
       <c r="N4" t="n">
-        <v>28.1469836065574</v>
+        <v>28.42293442622952</v>
       </c>
       <c r="O4" t="n">
-        <v>25.99829508196722</v>
+        <v>26.25318032786886</v>
       </c>
       <c r="P4" t="n">
-        <v>22.24603278688523</v>
+        <v>22.46413114754097</v>
       </c>
       <c r="Q4" t="n">
-        <v>15.402</v>
+        <v>15.553</v>
       </c>
       <c r="R4" t="n">
-        <v>8.270360655737703</v>
+        <v>8.351442622950817</v>
       </c>
       <c r="S4" t="n">
-        <v>3.205475409836064</v>
+        <v>3.236901639344261</v>
       </c>
       <c r="T4" t="n">
-        <v>0.785901639344262</v>
+        <v>0.7936065573770489</v>
       </c>
       <c r="U4" t="n">
-        <v>0.01003278688524591</v>
+        <v>0.01013114754098362</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -31328,49 +31328,49 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4100502512562811</v>
+        <v>0.4140703517587936</v>
       </c>
       <c r="H5" t="n">
-        <v>4.199427135678389</v>
+        <v>4.240597989949746</v>
       </c>
       <c r="I5" t="n">
-        <v>15.80846231155779</v>
+        <v>15.96344723618091</v>
       </c>
       <c r="J5" t="n">
-        <v>34.80250251256282</v>
+        <v>35.14370351758794</v>
       </c>
       <c r="K5" t="n">
-        <v>52.15992964824121</v>
+        <v>52.67130150753769</v>
       </c>
       <c r="L5" t="n">
-        <v>64.70900502512563</v>
+        <v>65.34340703517589</v>
       </c>
       <c r="M5" t="n">
-        <v>72.00123618090453</v>
+        <v>72.70713065326633</v>
       </c>
       <c r="N5" t="n">
-        <v>73.16629145728643</v>
+        <v>73.88360804020101</v>
       </c>
       <c r="O5" t="n">
-        <v>69.08885427135678</v>
+        <v>69.76619597989949</v>
       </c>
       <c r="P5" t="n">
-        <v>58.96573869346734</v>
+        <v>59.54383417085427</v>
       </c>
       <c r="Q5" t="n">
-        <v>44.28081407035176</v>
+        <v>44.71493969849246</v>
       </c>
       <c r="R5" t="n">
-        <v>25.75781909547739</v>
+        <v>26.01034673366835</v>
       </c>
       <c r="S5" t="n">
-        <v>9.344020100502515</v>
+        <v>9.435628140703519</v>
       </c>
       <c r="T5" t="n">
-        <v>1.794994974874371</v>
+        <v>1.81259296482412</v>
       </c>
       <c r="U5" t="n">
-        <v>0.03280402010050248</v>
+        <v>0.03312562814070349</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -31407,49 +31407,49 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2193962264150943</v>
+        <v>0.2215471698113208</v>
       </c>
       <c r="H6" t="n">
-        <v>2.118905660377359</v>
+        <v>2.139679245283019</v>
       </c>
       <c r="I6" t="n">
-        <v>7.553773584905661</v>
+        <v>7.627830188679247</v>
       </c>
       <c r="J6" t="n">
-        <v>20.7281320754717</v>
+        <v>20.93134905660378</v>
       </c>
       <c r="K6" t="n">
-        <v>35.42767924528302</v>
+        <v>35.77500943396227</v>
       </c>
       <c r="L6" t="n">
-        <v>47.63688679245283</v>
+        <v>48.10391509433963</v>
       </c>
       <c r="M6" t="n">
-        <v>55.58999999999999</v>
+        <v>56.13499999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>57.06130188679246</v>
+        <v>57.62072641509435</v>
       </c>
       <c r="O6" t="n">
-        <v>52.19994339622642</v>
+        <v>52.71170754716981</v>
       </c>
       <c r="P6" t="n">
-        <v>41.89505660377359</v>
+        <v>42.3057924528302</v>
       </c>
       <c r="Q6" t="n">
-        <v>28.00573584905661</v>
+        <v>28.28030188679246</v>
       </c>
       <c r="R6" t="n">
-        <v>13.62181132075472</v>
+        <v>13.75535849056604</v>
       </c>
       <c r="S6" t="n">
-        <v>4.07518867924528</v>
+        <v>4.115141509433959</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8843207547169808</v>
+        <v>0.8929905660377355</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01443396226415095</v>
+        <v>0.01457547169811321</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -31486,49 +31486,49 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1839344262295082</v>
+        <v>0.1857377049180328</v>
       </c>
       <c r="H7" t="n">
-        <v>1.635344262295083</v>
+        <v>1.651377049180329</v>
       </c>
       <c r="I7" t="n">
-        <v>5.531409836065575</v>
+        <v>5.585639344262296</v>
       </c>
       <c r="J7" t="n">
-        <v>13.00416393442623</v>
+        <v>13.13165573770492</v>
       </c>
       <c r="K7" t="n">
-        <v>21.36983606557376</v>
+        <v>21.57934426229507</v>
       </c>
       <c r="L7" t="n">
-        <v>27.34603278688525</v>
+        <v>27.61413114754098</v>
       </c>
       <c r="M7" t="n">
-        <v>28.83255737704917</v>
+        <v>29.11522950819672</v>
       </c>
       <c r="N7" t="n">
-        <v>28.1469836065574</v>
+        <v>28.42293442622952</v>
       </c>
       <c r="O7" t="n">
-        <v>25.99829508196722</v>
+        <v>26.25318032786886</v>
       </c>
       <c r="P7" t="n">
-        <v>22.24603278688523</v>
+        <v>22.46413114754097</v>
       </c>
       <c r="Q7" t="n">
-        <v>15.402</v>
+        <v>15.553</v>
       </c>
       <c r="R7" t="n">
-        <v>8.270360655737703</v>
+        <v>8.351442622950817</v>
       </c>
       <c r="S7" t="n">
-        <v>3.205475409836064</v>
+        <v>3.236901639344261</v>
       </c>
       <c r="T7" t="n">
-        <v>0.785901639344262</v>
+        <v>0.7936065573770489</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01003278688524591</v>
+        <v>0.01013114754098362</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -34743,25 +34743,25 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>358.8888888888889</v>
+        <v>0.1006972724976123</v>
       </c>
       <c r="K2" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="L2" t="n">
-        <v>374</v>
+        <v>298.5718215266224</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>373</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>373</v>
       </c>
       <c r="P2" t="n">
-        <v>374</v>
+        <v>59.25677413017286</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -34822,25 +34822,25 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>145.9367383131474</v>
+        <v>142.3822933058607</v>
       </c>
       <c r="K3" t="n">
-        <v>226.5315338860743</v>
+        <v>226.8788640747536</v>
       </c>
       <c r="L3" t="n">
-        <v>321.7282621411399</v>
+        <v>322.1952904430266</v>
       </c>
       <c r="M3" t="n">
-        <v>142.5400421645043</v>
+        <v>143.0850421645043</v>
       </c>
       <c r="N3" t="n">
-        <v>191.6878519954473</v>
+        <v>192.2472765237492</v>
       </c>
       <c r="O3" t="n">
-        <v>293.6569652989728</v>
+        <v>294.1687294499162</v>
       </c>
       <c r="P3" t="n">
-        <v>155.5610611184268</v>
+        <v>155.9717969674834</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -34877,37 +34877,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>68.6693832765239</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>155.141864863388</v>
       </c>
       <c r="H4" t="n">
-        <v>172.8642181606765</v>
+        <v>172.8802509475617</v>
       </c>
       <c r="I4" t="n">
-        <v>228.8979542159473</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>132.8490622644307</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>3.798404629106074</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -34928,22 +34928,22 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>40.83199570698065</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>190.7613351330866</v>
+        <v>190.7690400511193</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>249.0517398730831</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X4" t="n">
-        <v>113.6396670599086</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -34980,28 +34980,28 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>0.1006972724976123</v>
       </c>
       <c r="K5" t="n">
         <v>374</v>
       </c>
       <c r="L5" t="n">
-        <v>373.9999999999999</v>
+        <v>374</v>
       </c>
       <c r="M5" t="n">
+        <v>299.5314174862184</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>59.25677413017286</v>
+      </c>
+      <c r="Q5" t="n">
         <v>374</v>
-      </c>
-      <c r="N5" t="n">
-        <v>300.2102102361032</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>58.67867865278593</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35059,25 +35059,25 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>145.9367383131474</v>
+        <v>146.1399552942795</v>
       </c>
       <c r="K6" t="n">
-        <v>226.5315338860743</v>
+        <v>226.8788640747536</v>
       </c>
       <c r="L6" t="n">
-        <v>321.7282621411399</v>
+        <v>322.1952904430266</v>
       </c>
       <c r="M6" t="n">
-        <v>142.5400421645043</v>
+        <v>143.0850421645043</v>
       </c>
       <c r="N6" t="n">
-        <v>191.6878519954473</v>
+        <v>192.2472765237492</v>
       </c>
       <c r="O6" t="n">
-        <v>293.6569652989728</v>
+        <v>294.1687294499162</v>
       </c>
       <c r="P6" t="n">
-        <v>155.5610611184268</v>
+        <v>155.9717969674834</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -35114,37 +35114,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E7" t="n">
         <v>119.0190951630435</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G7" t="n">
-        <v>155.1400615846995</v>
+        <v>155.141864863388</v>
       </c>
       <c r="H7" t="n">
-        <v>172.8642181606765</v>
+        <v>172.8802509475617</v>
       </c>
       <c r="I7" t="n">
-        <v>228.8979542159473</v>
+        <v>228.952183724144</v>
       </c>
       <c r="J7" t="n">
-        <v>374</v>
+        <v>79.94564616184368</v>
       </c>
       <c r="K7" t="n">
-        <v>132.8490622644307</v>
+        <v>133.058570461152</v>
       </c>
       <c r="L7" t="n">
-        <v>3.798404629106074</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -35171,7 +35171,7 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>31.40368624526177</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -35180,7 +35180,7 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
@@ -35220,7 +35220,7 @@
         <v>0.1006972724976123</v>
       </c>
       <c r="K8" t="n">
-        <v>358.7881916163914</v>
+        <v>374</v>
       </c>
       <c r="L8" t="n">
         <v>374</v>
@@ -35229,13 +35229,13 @@
         <v>374</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>299.5314174862185</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>374</v>
+        <v>59.25677413017286</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -35357,25 +35357,25 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>155.141864863388</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>172.8802509475617</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>374</v>
+        <v>364.9828198001628</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -35402,19 +35402,19 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>40.86342193648881</v>
       </c>
       <c r="T10" t="n">
-        <v>190.7690400511193</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>249.0517398730831</v>
       </c>
       <c r="V10" t="n">
-        <v>125.4103436049263</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -35454,25 +35454,25 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>512.6348760697097</v>
+        <v>82.3301394835529</v>
       </c>
       <c r="K11" t="n">
-        <v>648.9999999999999</v>
+        <v>649</v>
       </c>
       <c r="L11" t="n">
         <v>649</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>179.1121759491996</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="O11" t="n">
         <v>162.757678164601</v>
       </c>
       <c r="P11" t="n">
-        <v>596.3852235434673</v>
+        <v>198.5777841804241</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -35606,7 +35606,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H13" t="n">
-        <v>97.74415258690598</v>
+        <v>97.74415258690597</v>
       </c>
       <c r="I13" t="n">
         <v>163.0214951995539</v>
@@ -35694,7 +35694,7 @@
         <v>512.6348760697097</v>
       </c>
       <c r="K14" t="n">
-        <v>648.9999999999999</v>
+        <v>454.4388343405527</v>
       </c>
       <c r="L14" t="n">
         <v>649</v>
@@ -35712,7 +35712,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q14" t="n">
-        <v>397.8074393630433</v>
+        <v>592.3686050224903</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35843,7 +35843,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H16" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I16" t="n">
         <v>163.0214951995539</v>
@@ -35928,28 +35928,28 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>512.6348760697097</v>
+        <v>82.3301394835529</v>
       </c>
       <c r="K17" t="n">
-        <v>648.9999999999999</v>
+        <v>649</v>
       </c>
       <c r="L17" t="n">
-        <v>218.2342914572864</v>
+        <v>649</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>179.1121759491996</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="O17" t="n">
         <v>162.757678164601</v>
       </c>
       <c r="P17" t="n">
-        <v>434.7823270636906</v>
+        <v>198.5777841804241</v>
       </c>
       <c r="Q17" t="n">
-        <v>592.3686050224903</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36165,19 +36165,19 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K20" t="n">
-        <v>179.1121759491997</v>
+        <v>648.9999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>649</v>
+        <v>454.4388343405528</v>
       </c>
       <c r="M20" t="n">
-        <v>649</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>649</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>162.757678164601</v>
@@ -36186,7 +36186,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>592.3686050224903</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36317,7 +36317,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H22" t="n">
-        <v>97.74415258690598</v>
+        <v>97.74415258690597</v>
       </c>
       <c r="I22" t="n">
         <v>163.0214951995539</v>
@@ -36411,13 +36411,13 @@
         <v>649</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>179.1121759491996</v>
       </c>
       <c r="N23" t="n">
         <v>649</v>
       </c>
       <c r="O23" t="n">
-        <v>341.8698541138006</v>
+        <v>162.757678164601</v>
       </c>
       <c r="P23" t="n">
         <v>198.5777841804241</v>
@@ -36554,7 +36554,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H25" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I25" t="n">
         <v>163.0214951995539</v>
@@ -36642,19 +36642,19 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K26" t="n">
+        <v>175.9119195979899</v>
+      </c>
+      <c r="L26" t="n">
+        <v>218.2342914572864</v>
+      </c>
+      <c r="M26" t="n">
+        <v>596.7236430585245</v>
+      </c>
+      <c r="N26" t="n">
         <v>649</v>
       </c>
-      <c r="L26" t="n">
+      <c r="O26" t="n">
         <v>649</v>
-      </c>
-      <c r="M26" t="n">
-        <v>649</v>
-      </c>
-      <c r="N26" t="n">
-        <v>179.1121759491994</v>
-      </c>
-      <c r="O26" t="n">
-        <v>162.757678164601</v>
       </c>
       <c r="P26" t="n">
         <v>198.5777841804241</v>
@@ -36879,25 +36879,25 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K29" t="n">
-        <v>175.9119195979899</v>
+        <v>649</v>
       </c>
       <c r="L29" t="n">
-        <v>218.2342914572864</v>
+        <v>649</v>
       </c>
       <c r="M29" t="n">
-        <v>202.9328222164582</v>
+        <v>649</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>179.1121759491994</v>
       </c>
       <c r="O29" t="n">
-        <v>649</v>
+        <v>162.757678164601</v>
       </c>
       <c r="P29" t="n">
-        <v>649</v>
+        <v>198.5777841804241</v>
       </c>
       <c r="Q29" t="n">
-        <v>592.3686050224903</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -37028,7 +37028,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H31" t="n">
-        <v>97.74415258690598</v>
+        <v>97.74415258690597</v>
       </c>
       <c r="I31" t="n">
         <v>163.0214951995539</v>
@@ -37122,10 +37122,10 @@
         <v>649</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="N32" t="n">
-        <v>235.7435709267093</v>
+        <v>179.1121759491994</v>
       </c>
       <c r="O32" t="n">
         <v>162.757678164601</v>
@@ -37134,7 +37134,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q32" t="n">
-        <v>592.3686050224903</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37353,13 +37353,13 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K35" t="n">
-        <v>649</v>
+        <v>235.7435709267094</v>
       </c>
       <c r="L35" t="n">
         <v>649</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -37368,7 +37368,7 @@
         <v>162.757678164601</v>
       </c>
       <c r="P35" t="n">
-        <v>434.3213551071335</v>
+        <v>198.5777841804241</v>
       </c>
       <c r="Q35" t="n">
         <v>592.3686050224903</v>
@@ -37587,16 +37587,16 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>512.6348760697097</v>
+        <v>82.3301394835529</v>
       </c>
       <c r="K38" t="n">
-        <v>175.9119195979899</v>
+        <v>649</v>
       </c>
       <c r="L38" t="n">
-        <v>218.2342914572864</v>
+        <v>649</v>
       </c>
       <c r="M38" t="n">
-        <v>258.8704074657004</v>
+        <v>235.7435709267093</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
@@ -37605,7 +37605,7 @@
         <v>162.757678164601</v>
       </c>
       <c r="P38" t="n">
-        <v>649</v>
+        <v>198.5777841804241</v>
       </c>
       <c r="Q38" t="n">
         <v>592.3686050224903</v>
@@ -37827,25 +37827,25 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K41" t="n">
-        <v>175.9119195979899</v>
+        <v>649</v>
       </c>
       <c r="L41" t="n">
-        <v>218.2342914572864</v>
+        <v>235.7435709267094</v>
       </c>
       <c r="M41" t="n">
-        <v>596.7236430585245</v>
+        <v>649</v>
       </c>
       <c r="N41" t="n">
-        <v>649</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>649</v>
+        <v>162.757678164601</v>
       </c>
       <c r="P41" t="n">
         <v>198.5777841804241</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>592.3686050224903</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37976,7 +37976,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H43" t="n">
-        <v>97.74415258690598</v>
+        <v>97.74415258690597</v>
       </c>
       <c r="I43" t="n">
         <v>163.0214951995539</v>
@@ -38061,28 +38061,28 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K44" t="n">
+        <v>175.9119195979899</v>
+      </c>
+      <c r="L44" t="n">
+        <v>278.5269147425627</v>
+      </c>
+      <c r="M44" t="n">
         <v>649</v>
       </c>
-      <c r="L44" t="n">
-        <v>649</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
       <c r="N44" t="n">
-        <v>341.8698541138008</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>649</v>
+        <v>162.757678164601</v>
       </c>
       <c r="P44" t="n">
         <v>198.5777841804241</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>592.3686050224903</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38213,7 +38213,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H46" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I46" t="n">
         <v>163.0214951995539</v>
